--- a/xlsx/shosta.xlsx
+++ b/xlsx/shosta.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Parker\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Parker\WebstormProjects\konzert-public-data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -41,34 +41,34 @@
     <t>sort</t>
   </si>
   <si>
-    <t>opus</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>title-org</t>
-  </si>
-  <si>
-    <t>place</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>part</t>
-  </si>
-  <si>
-    <t>inst</t>
-  </si>
-  <si>
-    <t>status</t>
+    <t>Opus</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Original Title</t>
+  </si>
+  <si>
+    <t>Place</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
   <si>
     <t>Dedication</t>
   </si>
   <si>
-    <t>note</t>
+    <t>Note</t>
   </si>
   <si>
     <t>Scherzo in F-sharp minor, op. 1</t>
@@ -394,8 +394,7 @@
     <t>1925/12/30 – 1927/8</t>
   </si>
   <si>
-    <t>One movement: Largo (q = 46) · [Allegro molto] (q = 152) · Poco meno mosso
-(q = 138) · Allegro molto (q = 192) · Meno mosso (q = 100) · Moderato</t>
+    <t>One movement: Largo (q = 46) · [Allegro molto] (q = 152) · Poco meno mosso (q = 138) · Allegro molto (q = 192) · Meno mosso (q = 100) · Moderato</t>
   </si>
   <si>
     <t>orchestra with mixed choir
@@ -499,18 +498,13 @@
     <t>1928/12-1929/3</t>
   </si>
   <si>
-    <t>reel no. 1 ‘General Sale’Allegro 
-non troppo · Allegro · Andantino · Allegro · Andantino · Allegro · Andante
-reel no. 2 ‘Head Over Heels’Allegro moderato · Andantino · Al
-legro vivo
-reel no. 3 ‘The Siege of Paris’Largo · Allegro · Largo
-reel no. 4 ‘18 March 1871’Andante · Allegro · Andante · Più mosso · Allegro · Molto meno mosso · 
-Allegretto · [Andante semplice] · Adagio
-reel no. 5 ‘Versailles Against Paris’Allegretto · Allegro · Andante · Allegro moderato
-reel no. 6 ‘The Barricade’Adagio · Allegro moderato · Allegretto · Scherzando · Al
-legro [con] brio · Andante semplice · Allegro [con] brio
-Reel No. 7 ‘To the Firing Squad’[Andante] · Allegro · Andante ·  
-Adagio · Allegro · Andante
+    <t>Reel No. 1 ‘General Sale’Allegro non troppo · Allegro · Andantino · Allegro · Andantino · Allegro · Andante
+Reel No. 2 ‘Head Over Heels’Allegro moderato · Andantino · Allegro vivo
+Reel No. 3 ‘The Siege of Paris’Largo · Allegro · Largo
+Reel No. 4 ‘18 March 1871’Andante · Allegro · Andante · Più mosso · Allegro · Molto meno mosso · Allegretto · [Andante semplice] · Adagio
+Reel No. 5 ‘Versailles Against Paris’Allegretto · Allegro · Andante · Allegro moderato
+Reel No. 6 ‘The Barricade’Adagio · Allegro moderato · Allegretto · Scherzando · Allegro [con] brio · Andante semplice · Allegro [con] brio
+Reel No. 7 ‘To the Firing Squad’[Andante] · Allegro · Andante ·  Adagio · Allegro · Andante
 Reel No. 8 ‘Death’Largo · Allegro appassionato</t>
   </si>
   <si>
@@ -566,8 +560,7 @@
 10. Fire
 11. Fire Signals
 12. Firemen’s Chorus Marciale
-13. Symphonic Entr’act Allegro [music from Nos. 4 and 10, not included in the
-staging]
+13. Symphonic Entr’act Allegro [music from Nos. 4 and 10, not included in the staging]
 14. March of the Pioneers Allegretto [not included in the staging]
 15. March of the City-Elders Tempo di marcia
 16. Flourish Allegro
@@ -618,9 +611,7 @@
     <t>1929/4 – 1929/10</t>
   </si>
   <si>
-    <t>One movement: Allegretto · Allegro · Più mosso · Meno mosso · Allegro · 
-Andante · Allegro · Poco meno mosso · Largo · Allegro molto · Meno mosso · 
-Andante · Largo · Moderato · Più mosso</t>
+    <t>One movement: Allegretto · Allegro · Più mosso · Meno mosso · Allegro · Andante · Allegro · Poco meno mosso · Largo · Allegro molto · Meno mosso · Andante · Largo · Moderato · Più mosso</t>
   </si>
   <si>
     <t>orchestra with mixed choir
@@ -684,11 +675,10 @@
     <t>1930, revised 1935</t>
   </si>
   <si>
-    <t>1. Introduction [Nos. 1 and 2] Allegro non troppo (q = 112) · Allegretto (q = 168) ·
-q = 120 · Più mosso (h = 92) · q = 168
+    <t>1. Introduction [Nos. 1 and 2] Allegro non troppo (q = 112) · Allegretto (q = 168) · q = 120 · Più mosso (h = 92) · q = 168
 2. Adagio [No. 9] q = 72
 3. Polka [No. 30] Allegretto (q = 84) · Presto (q = 208)
-4.  Dance [No. 11] Allegro (q = 144)</t>
+4. Dance [No. 11] Allegro (q = 144)</t>
   </si>
   <si>
     <t>1.picc.1.corA.1.Ebcl.bcl.ssax.1.dbn-4.barhn.3.3.1-timp.perc:tgl/wdbl/
@@ -770,7 +760,7 @@
     <t>1930/9/17–1931/3/9</t>
   </si>
   <si>
-    <t>7 reels</t>
+    <t>7 Reels</t>
   </si>
   <si>
     <t>3(III=picc).3(III=corA).4(III=Ebcl,IV=bcl).3(III=dbn)-4.2.3.1-timp.
@@ -809,11 +799,9 @@
   </si>
   <si>
     <t>1. Overture Adagio · Allegro [No. 1]
-2. Polka Allegretto · Allegro · Moderato · Allegretto · Più mosso · Allegretto ·
-Allegro [No. 11]
+2. Polka Allegretto · Allegro · Moderato · Allegretto · Più mosso · Allegretto ·Allegro [No. 11]
 3. Variation Moderato non troppo [No. 38]
-4. Tango Allegretto · Andante · Più mosso · Più mosso · Allegretto · Allegro ·
-Meno mosso · Allegro [No. 29]
+4. Tango Allegretto · Andante · Più mosso · Più mosso · Allegretto · Allegro ·Meno mosso · Allegro [No. 29]
 5. Intermezzo Allegretto [No. 10]
 6. Finale Allegro [No. 43]</t>
   </si>
@@ -883,8 +871,7 @@
   </si>
   <si>
     <t>1. Allegro con brio
-2. Presto · Allegretto · Moderato · Presto · Moderato · Presto · Moderato ·
-Adagio · Allegro
+2. Presto · Allegretto · Moderato · Presto · Moderato · Presto · Moderato ·Adagio · Allegro
 3. Allegretto</t>
   </si>
   <si>
@@ -1028,16 +1015,14 @@
 2. Galop Allegro [No. 7] 
 3. Transition to the Field [Allegro  (q = 100)] [No. 8] attacca
 4. The Field [A Landscape] Andantino [No. 9]
-5. Introduction to Act II. Petrushka Allegro · L’istesso tempo [No. 16a]
-Garmoshka L’istesso tempo [No. 17]
+5. Introduction to Act II. Petrushka Allegro · L’istesso tempo [No. 16a] Garmoshka L’istesso tempo [No. 17]
 6. The Storm Allegro [No. 17b]
 7. The Arrival of the Lorry Allegro [No. 18] attacca
 8. Dance Andante · Allegro [No. 18a]
 9. Transition to the Kitchen (Jugglers and Waitresses) Allegretto (Allegro) [Nos.
 19, 21]
 10. Waitresses Allegro [No. 21a]
-11. Paradise. Flight of the Cherubim Allegretto [No. 26]
-Flight of the Angels L’istesso tempo [No. 27]
+11. Paradise. Flight of the Cherubim Allegretto [No. 26] Flight of the Angels L’istesso tempo [No. 27]
 12. Adagio [No. 28]
 13. Bacchanalia of John of Kronstadt and Paraskeva Pyatnitsa Presto [(No. 29)]
 14. Waltz Moderato [(No. 29a)]
@@ -1045,8 +1030,7 @@
 16. Polka Con moto [No. 11]
 17. March (Camouflage) Allegretto [No. 12]
 18. River-Bed Moderato · Molto più mosso [No. 15]
-19. Finale to Act I: Dance of the Temporary Conquerors Moderato · Più allegro al
-fine [No. 16]</t>
+19. Finale to Act I: Dance of the Temporary Conquerors Moderato · Più allegro al fine [No. 16]</t>
   </si>
   <si>
     <t>1.picc.1.1.bcl.2.ssax.tsax-1.2.2.1-timp.perc(4/5):tgl/SD/TD/BD/sus,cym/
@@ -1091,8 +1075,7 @@
     <t>1932</t>
   </si>
   <si>
-    <t>1. Introduction and Night Patrol Allegro non troppo · Moderato. Poco allegretto
-[Nos. 1, 2]
+    <t>1. Introduction and Night Patrol Allegro non troppo · Moderato. Poco allegretto [Nos. 1, 2]
 2. Funeral March Adagio [No. 4]
 3. Flourish and Dancing Music Allegro [Nos. 7, 8]
 4. The Hunt Allegro [No. 16]
@@ -1100,8 +1083,7 @@
 6. Procession Moderato [No. 25 = ‘Entrance of the Guests’]
 7. Musical Pantomime Allegro [No. 29 = ‘Pantomime’]
 8. The Banquet Allegro [No. 38 = ‘Can-can’]
-9. Ophelia’s Song Allegro · Meno mosso · Meno mosso · Meno mosso · Presto
-[No. 39]
+9. Ophelia’s Song Allegro · Meno mosso · Meno mosso · Meno mosso · Presto [No. 39]
 10. Lullaby Andantino [No. 41]
 11. Requiem Adagio [No. 44]
 12. The Tournament Allegro [No. 45]
@@ -1385,10 +1367,8 @@
   </si>
   <si>
     <t>1. Introduction Moderato [string quartet]
-2. The Year 1914: The workers’ residential block and factory gates Allegretto
-[string quartet]
-3. The families wait for the strikers to return Allegretto [string quartet, trumpet,
-piano]
+2. The Year 1914: The workers’ residential block and factory gates Allegretto [string quartet]
+3. The families wait for the strikers to return Allegretto [string quartet, trumpet, piano]
 4. ‘The Keys to Happiness’ Allegretto moderato [string quartet, trumpet, piano]
 5. The children attempt to sing their ‘poppy song’ Allegretto [ensemble]*
 6. By the river: Revolutionary song ‘Tormented by Lack of Freedom’ [solo voices]*
@@ -1404,8 +1384,7 @@
 16. The Forester’s Hut Andante [piano, string quartet]
 17. Fanfare: Andrei arrives with news from the front [2 trumpets, side drum]*
 18. Fanfare [two trumpets]*
-19. The girls find a chicken Allegro [piano, trumpet, string quartet, music not
-used in the film, which may represent the original opening music]
+19. The girls find a chicken Allegro [piano, trumpet, string quartet, music not used in the film, which may represent the original opening music]
 20. Natasha and Zoya sing: ‘Where are those warm nights?’*
 21. Natasha and Zoya are rescued Allegro molto [full orchestra]*
 22. Fanfare: Andrei and Senka arrive [2 trumpets]*
@@ -1450,8 +1429,7 @@
     <t>1935/9/13–1936/4/26</t>
   </si>
   <si>
-    <t>1. Allegro poco moderato (q = 92) · q = 54 · e = 108 · e = 138 · e = 60 · e = 108 · Presto
-(q = 168) · q = 184 · q = 69 · q = 92 · e = 60 · q = 108 · q = 72 · e = 69
+    <t>1. Allegro poco moderato (q = 92) · q = 54 · e = 108 · e = 138 · e = 60 · e = 108 · Presto (q = 168) · q = 184 · q = 69 · q = 92 · e = 60 · q = 108 · q = 72 · e = 69
 2. Moderato con moto (e = 144)
 3. Largo (q = 69) · Allegro (h k = 84) · q = 126 · q = 184 · q = 100 · h k = 100 · h k = 50</t>
   </si>
@@ -1647,8 +1625,7 @@
 Соч. 50a</t>
   </si>
   <si>
-    <t>1. Prelude (‘Boldly, Friends, on we March!’) Moderato · Allegro non troppo ·
-Adagio
+    <t>1. Prelude (‘Boldly, Friends, on we March!’) Moderato · Allegro non troppo · Adagio
 2. Attack Sequence Allegro
 3. Death of the Old Worker Adagio
 4. Waltz Allegro sostenuto
@@ -1714,8 +1691,7 @@
     <t>1939/7–1939/10</t>
   </si>
   <si>
-    <t>1. Largo (e = 72) · q = 44 · Poco più mosso e poco rubato (q = 52) · Moderato (q = 66) ·
-Sostenuto · q = 52 · Sostenuto · Largo (q = 44)
+    <t>1. Largo (e = 72) · q = 44 · Poco più mosso e poco rubato (q = 52) · Moderato (q = 66) · Sostenuto · q = 52 · Sostenuto · Largo (q = 44)
 2. Allegro (q = 88-96)
 3. Presto (h = 152)</t>
   </si>
@@ -1745,9 +1721,7 @@
     <t>1939 Spring</t>
   </si>
   <si>
-    <t>Allegretto (q = 80) · Moderato (q = 60) · Allegro (q = 152) · Moderato con moto (q = 76) ·
-Presto (h = 120) · Moderato (q = 60) · Allegro (h = 60) · Moderato (q = 60) · Allegro 
-(q = h) · Moderato (q = 60) · q = 120 · q = 60</t>
+    <t>Allegretto (q = 80) · Moderato (q = 60) · Allegro (q = 152) · Moderato con moto (q = 76) · Presto (h = 120) · Moderato (q = 60) · Allegro (h = 60) · Moderato (q = 60) · Allegro (q = h) · Moderato (q = 60) · q = 120 · q = 60</t>
   </si>
   <si>
     <t>2(II=picc).2(II=corA).2(II=bcl).2(II=dbn)-4.2.2.0-timp.perc:tgl/wdbl/tamb/SD/
@@ -1791,21 +1765,18 @@
   <si>
     <t>prologue
 1. Scene 1 ‘Courtyard of the Moscow Novodevichy Convent’
-2. Scene 2 ‘Yard in the Moscow Kremlin. Entrance of the Tsar’s appartments.
-solemn sound of the bells’
+2. Scene 2 ‘Yard in the Moscow Kremlin. Entrance of the Tsar’s appartments. solemn sound of the bells’
 act i
 3. Scene 3 ‘Cell in the Chudovi Monastery. Night’
 4. Scene 4 ‘Inn at the Lithuanian border’
 act ii
-5. Scene 5 ‘The Tsar’s appartment in the Moscow Kremlin’ (first and second
-redaction)
+5. Scene 5 ‘The Tsar’s appartment in the Moscow Kremlin’ (first and second redaction)
 act iii
 6. Scene 6 ‘Sandomir Castle. Marina Mnishek at the dressing table. Girls’
 7. Scene 7 ‘Sandomir Castle. Garden. Fountain. Moonlit night’
 act iv
 8. Scene 8 ‘Square in front of St. Basil’s Cathedral. Crowd of the poor.
-9. Scene 9 ‘The Granovitaya Palata in the Moscow Kremlin: The boyars’ extra
-ordinary meeting’
+9. Scene 9 ‘The Granovitaya Palata in the Moscow Kremlin: The boyars’ extraordinary meeting’
 10. Scene 10 ‘Clearing near Kromy. Night’</t>
   </si>
   <si>
@@ -1892,12 +1863,9 @@
     <t>1941/7/19 – 1941/12/27</t>
   </si>
   <si>
-    <t>1. Allegretto (q = 116) · Poco più mosso (q = 126) · Poco più mosso (q = 108) · Meno
-mosso (q = 69) · Poco più mosso (q = 92) · Allegretto (q = 126)
+    <t>1. Allegretto (q = 116) · Poco più mosso (q = 126) · Poco più mosso (q = 108) · Meno mosso (q = 69) · Poco più mosso (q = 92) · Allegretto (q = 126)
 2. Moderato (poco allegretto) (q = 96)
-3. Adagio (q = 112) · Largo (q = 92) · Adagio (q = 112) · Largo (q = 92) · Adagio
-(q = 112) · Largo (q = 92) · Moderato risoluto (q = 120) · Largo (q = 92) · q = 120 ·
-Largo (q = 92) · Adagio (q = 112) · Largo (q = 92) · Adagio (q = 112) attacca
+3. Adagio (q = 112) · Largo (q = 92) · Adagio (q = 112) · Largo (q = 92) · Adagio (q = 112) · Largo (q = 92) · Moderato risoluto (q = 120) · Largo (q = 92) · q = 120 · Largo (q = 92) · Adagio (q = 112) · Largo (q = 92) · Adagio (q = 112) attacca
 4. Allegro non troppo (h = 132) · Moderato (q = 100)</t>
   </si>
   <si>
@@ -2241,8 +2209,7 @@
     <t>1. A minor Allegro moderato e scherzando [No. 5 from op. 2]
 2. G major Andante [No. 2 from op. 2]
 3. E minor Allegro moderato [No. 3 from op. 2]
-4. D flat major Moderato · Andante amoroso · Moderato · Andante cantabile
-[No. 7 from op. 2]
+4. D flat major Moderato · Andante amoroso · Moderato · Andante cantabile [No. 7 from op. 2]
 5. F minor Andantino [No. 6 from op. 2]</t>
   </si>
   <si>
@@ -2264,15 +2231,13 @@
     <t>Семь фуг</t>
   </si>
   <si>
-    <t>| Fugue | Key | voci | 含义 |
-|---|---|---:|---|
-| 1 | C major | 2 | 2声部赋格 |
-| 2 | F major | 4 | 4声部赋格 |
-| 3 | E minor | 4 | 4声部赋格 |
-| 4 | D minor | 4 | 4声部赋格 |
-| 5 | C minor | 4 incomplete | 4声部，但未完成 |
-| 6 | D major | 4 incomplete | 4声部，但未完成 |
-| 7 | C minor | 4 incomplete | 4声部，但未完成 |</t>
+    <t>| 1 | C major | 2            |
+| 2 | F major | 4            |
+| 3 | E minor | 4            |
+| 4 | D minor | 4            |
+| 5 | C minor | 4 incomplete |
+| 6 | D major | 4 incomplete |
+| 7 | C minor | 4 incomplete |</t>
   </si>
   <si>
     <t>Piano Piece in G major</t>
@@ -2537,13 +2502,10 @@
 5. [Nastya’s Dance] Allegro
 6. [Foreigners I and II, Veselchak, choir] Moderato
 7. [Zoologist] Alla marcia
-8. [Susanna, Foreigners I and II, Zoologist, Orango, Veselchak, choir] Allegro
-moderato · Meno mosso · Allegro
+8. [Susanna, Foreigners I and II, Zoologist, Orango, Veselchak, choir] Allegro moderato · Meno mosso · Allegro
 9. [Nastya’s taming dance] Allegretto · Adagio · Adagio · Allegretto · Allegretto
-10. [Susanna, Zoologist, Orango, Veselchak, Voice from the crowd, choir Ada
-gio · Andantino · Allegretto · Meno mosso
-11. [Renée, Armand, Paul, Veselchak, choir Allegretto · Tempo di valse · L’istesso
-tempo · Alla marcia · Presto</t>
+10. [Susanna, Zoologist, Orango, Veselchak, Voice from the crowd, choir Adagio · Andantino · Allegretto · Meno mosso
+11. [Renée, Armand, Paul, Veselchak, choir Allegretto · Tempo di valse · L’istesso tempo · Alla marcia · Presto</t>
   </si>
   <si>
     <t>2.picc.2.corA.2.Ebcl.ssax.asax.2.dbn-6.3.3.1-perc:timp/tgl/rattle/wdbl/cast/
@@ -2563,10 +2525,10 @@
     <t>1932/8</t>
   </si>
   <si>
+    <t>unfinished, lost</t>
+  </si>
+  <si>
     <t>Text by Nikolai Aseev</t>
-  </si>
-  <si>
-    <t>unfinished, lost</t>
   </si>
   <si>
     <t>Madrigal (Impromptu)</t>
@@ -2797,8 +2759,7 @@
   <si>
     <t>1. Introduction. Feast days are for lads like these ... Energico [instrumental] 
 2. The blue sky above me ... Giocoso · Meno mosso · Tempo I
-3. I went out into the grove on a summer’s night ... Lento non troppo
-[instrumental]
+3. I went out into the grove on a summer’s night ... Lento non troppo [instrumental]
 4. Here in our village ... Andante
 5. Dark red woodland berry ... Moderato, tempo giusto
 6. Oh, would I be free ... Allegretto
@@ -2828,6 +2789,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MiSans VF Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">(SONG OF THE FLEA) </t>
     </r>
     <r>
@@ -3700,7 +3668,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3734,9 +3702,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3744,64 +3709,22 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3815,17 +3738,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4410,123 +4327,123 @@
       <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16" t="s">
+      <c r="I2" s="14"/>
+      <c r="J2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="12"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" customHeight="1" spans="1:11">
       <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" customHeight="1" spans="1:11">
       <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <v>3</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="16" t="s">
+      <c r="I4" s="15"/>
+      <c r="J4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="21"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5" customHeight="1" spans="1:11">
       <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="16" t="s">
+      <c r="I5" s="15"/>
+      <c r="J5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4534,274 +4451,274 @@
       <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <v>5</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="16" t="s">
+      <c r="I6" s="15"/>
+      <c r="J6" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="21"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" customHeight="1" spans="1:11">
       <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>6</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="16" t="s">
+      <c r="I7" s="15"/>
+      <c r="J7" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="21"/>
+      <c r="K7" s="15"/>
     </row>
     <row r="8" customHeight="1" spans="1:11">
       <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <v>7</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="16" t="s">
+      <c r="I8" s="15"/>
+      <c r="J8" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K8" s="21"/>
+      <c r="K8" s="15"/>
     </row>
     <row r="9" customHeight="1" spans="1:11">
       <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>8</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="19"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="16" t="s">
+      <c r="H9" s="11"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="K9" s="21"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" customHeight="1" spans="1:11">
       <c r="A10" s="10">
         <v>9</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <v>9</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="23"/>
+      <c r="K10" s="11"/>
     </row>
     <row r="11" customHeight="1" spans="1:11">
       <c r="A11" s="10">
         <v>10</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>10</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="16" t="s">
+      <c r="I11" s="15"/>
+      <c r="J11" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="K11" s="21"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" customHeight="1" spans="1:11">
       <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <v>11</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="16" t="s">
+      <c r="H12" s="11"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="21"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13" customHeight="1" spans="1:11">
       <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>12</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="19"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="11"/>
     </row>
     <row r="14" customHeight="1" spans="1:11">
       <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <v>13</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G14" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="16" t="s">
+      <c r="I14" s="14"/>
+      <c r="J14" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="K14" s="11" t="s">
         <v>89</v>
       </c>
     </row>
@@ -4809,150 +4726,150 @@
       <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="16" t="s">
+      <c r="I15" s="15"/>
+      <c r="J15" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="K15" s="21"/>
+      <c r="K15" s="15"/>
     </row>
     <row r="16" customHeight="1" spans="1:11">
-      <c r="A16" s="27">
+      <c r="A16" s="17">
         <v>14</v>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="17">
         <v>14</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="12" t="s">
+      <c r="I16" s="15"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="11" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="27">
+      <c r="A17" s="17">
         <v>15</v>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="17">
         <v>15</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="12" t="s">
+      <c r="G17" s="13"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="11" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="27">
+      <c r="A18" s="17">
         <v>15.1</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="17"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="11"/>
     </row>
     <row r="19" customHeight="1" spans="1:11">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>16</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="41" t="s">
+      <c r="F19" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="16" t="s">
+      <c r="I19" s="14"/>
+      <c r="J19" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="K19" s="11" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4960,142 +4877,142 @@
       <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <v>17</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13" t="s">
+      <c r="E20" s="11"/>
+      <c r="F20" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="23" t="s">
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:11">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>18</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I21" s="20"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="12" t="s">
+      <c r="I21" s="15"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:11">
-      <c r="A22" s="27">
+      <c r="A22" s="17">
         <v>18.1</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="12"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="14" t="s">
+      <c r="E22" s="11"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="12" t="s">
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>19</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>19</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="12" t="s">
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:11">
-      <c r="A24" s="27">
+      <c r="A24" s="17">
         <v>19.1</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14" t="s">
+      <c r="E24" s="11"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="H24" s="19"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="12" t="s">
+      <c r="H24" s="11"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="11" t="s">
         <v>147</v>
       </c>
     </row>
@@ -5103,30 +5020,30 @@
       <c r="A25" s="10">
         <v>20</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>20</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="I25" s="21"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="12" t="s">
+      <c r="I25" s="15"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="11" t="s">
         <v>154</v>
       </c>
     </row>
@@ -5134,119 +5051,119 @@
       <c r="A26" s="10">
         <v>21</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <v>21</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I26" s="21"/>
-      <c r="J26" s="16" t="s">
+      <c r="I26" s="15"/>
+      <c r="J26" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="K26" s="23"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" customHeight="1" spans="1:11">
-      <c r="A27" s="11">
+      <c r="A27" s="10">
         <v>22</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>22</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G27" s="29"/>
-      <c r="H27" s="12" t="s">
+      <c r="G27" s="13"/>
+      <c r="H27" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="I27" s="15"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="12" t="s">
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:11">
-      <c r="A28" s="27">
+      <c r="A28" s="17">
         <v>22.1</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="19"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="11"/>
     </row>
     <row r="29" customHeight="1" spans="1:11">
       <c r="A29" s="10">
         <v>23</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>23</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="12" t="s">
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="11" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5254,30 +5171,30 @@
       <c r="A30" s="10">
         <v>24</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <v>24</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="I30" s="12"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="12" t="s">
+      <c r="I30" s="11"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="11" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5285,28 +5202,28 @@
       <c r="A31" s="10">
         <v>25</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>25</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="G31" s="29"/>
-      <c r="H31" s="12" t="s">
+      <c r="G31" s="13"/>
+      <c r="H31" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="12" t="s">
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="11" t="s">
         <v>188</v>
       </c>
     </row>
@@ -5314,30 +5231,30 @@
       <c r="A32" s="10">
         <v>26</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <v>26</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="G32" s="26" t="s">
+      <c r="G32" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="I32" s="21"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="12" t="s">
+      <c r="I32" s="15"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="11" t="s">
         <v>130</v>
       </c>
     </row>
@@ -5345,57 +5262,57 @@
       <c r="A33" s="10">
         <v>27</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>27</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="29"/>
-      <c r="H33" s="12" t="s">
+      <c r="G33" s="13"/>
+      <c r="H33" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="23" t="s">
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="11" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:11">
-      <c r="A34" s="27">
+      <c r="A34" s="17">
         <v>27.1</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="13" t="s">
+      <c r="E34" s="11"/>
+      <c r="F34" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="I34" s="21"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="12" t="s">
+      <c r="I34" s="15"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="11" t="s">
         <v>206</v>
       </c>
     </row>
@@ -5403,30 +5320,30 @@
       <c r="A35" s="10">
         <v>28</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>28</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="F35" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="I35" s="12"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="12" t="s">
+      <c r="I35" s="11"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="11" t="s">
         <v>212</v>
       </c>
     </row>
@@ -5434,119 +5351,119 @@
       <c r="A36" s="10">
         <v>29</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <v>29</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E36" s="12"/>
-      <c r="F36" s="13" t="s">
+      <c r="E36" s="11"/>
+      <c r="F36" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="G36" s="30"/>
-      <c r="H36" s="12" t="s">
+      <c r="G36" s="13"/>
+      <c r="H36" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="I36" s="15"/>
-      <c r="J36" s="16" t="s">
+      <c r="I36" s="14"/>
+      <c r="J36" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="K36" s="12" t="s">
+      <c r="K36" s="11" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:11">
-      <c r="A37" s="27">
+      <c r="A37" s="17">
         <v>29.1</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="E37" s="12"/>
-      <c r="F37" s="41" t="s">
+      <c r="E37" s="11"/>
+      <c r="F37" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="I37" s="21"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="17"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" customHeight="1" spans="1:11">
       <c r="A38" s="10">
         <v>30</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <v>30</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="H38" s="12" t="s">
+      <c r="H38" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="I38" s="21"/>
-      <c r="J38" s="16" t="s">
+      <c r="I38" s="15"/>
+      <c r="J38" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="K38" s="12" t="s">
+      <c r="K38" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:11">
-      <c r="A39" s="27">
+      <c r="A39" s="17">
         <v>30.1</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F39" s="41" t="s">
+      <c r="F39" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="I39" s="21"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="23" t="s">
+      <c r="I39" s="15"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="11" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5554,57 +5471,57 @@
       <c r="A40" s="10">
         <v>31</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <v>31</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F40" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="I40" s="12"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="12" t="s">
+      <c r="I40" s="11"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="11" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:11">
-      <c r="A41" s="27">
+      <c r="A41" s="17">
         <v>31.1</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="E41" s="12"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14" t="s">
+      <c r="E41" s="11"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="I41" s="21"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="12" t="s">
+      <c r="I41" s="15"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="11" t="s">
         <v>249</v>
       </c>
     </row>
@@ -5612,59 +5529,59 @@
       <c r="A42" s="10">
         <v>32</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="10">
         <v>32</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="G42" s="29"/>
-      <c r="H42" s="12" t="s">
+      <c r="G42" s="13"/>
+      <c r="H42" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="12" t="s">
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="11" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:11">
-      <c r="A43" s="27">
+      <c r="A43" s="17">
         <v>32.1</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="F43" s="41" t="s">
+      <c r="F43" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="I43" s="21"/>
-      <c r="J43" s="16"/>
-      <c r="K43" s="12" t="s">
+      <c r="I43" s="15"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="11" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5672,32 +5589,32 @@
       <c r="A44" s="10">
         <v>33</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <v>33</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F44" s="13" t="s">
+      <c r="F44" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="H44" s="23" t="s">
+      <c r="H44" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="I44" s="21"/>
-      <c r="J44" s="16" t="s">
+      <c r="I44" s="15"/>
+      <c r="J44" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="K44" s="23" t="s">
+      <c r="K44" s="11" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5705,113 +5622,113 @@
       <c r="A45" s="10">
         <v>34</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>34</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="17"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="11"/>
     </row>
     <row r="46" customHeight="1" spans="1:11">
       <c r="A46" s="10">
         <v>35</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <v>35</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="H46" s="12" t="s">
+      <c r="H46" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="I46" s="17"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="19"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="11"/>
     </row>
     <row r="47" customHeight="1" spans="1:11">
       <c r="A47" s="10">
         <v>36</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>36</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="G47" s="29"/>
-      <c r="H47" s="12" t="s">
+      <c r="G47" s="13"/>
+      <c r="H47" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="I47" s="21"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="12" t="s">
+      <c r="I47" s="15"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="11" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:11">
-      <c r="A48" s="27">
+      <c r="A48" s="17">
         <v>36.1</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="E48" s="12"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="14" t="s">
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="H48" s="12" t="s">
+      <c r="H48" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="I48" s="15"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="12" t="s">
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="11" t="s">
         <v>288</v>
       </c>
     </row>
@@ -5819,30 +5736,30 @@
       <c r="A49" s="10">
         <v>37</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>37</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="H49" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="12" t="s">
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="11" t="s">
         <v>294</v>
       </c>
     </row>
@@ -5850,2708 +5767,2707 @@
       <c r="A50" s="10">
         <v>38</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <v>38</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="F50" s="13" t="s">
+      <c r="F50" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="13" t="s">
         <v>299</v>
       </c>
-      <c r="H50" s="19"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="12" t="s">
+      <c r="H50" s="11"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:11">
-      <c r="A51" s="27">
+      <c r="A51" s="17">
         <v>39</v>
       </c>
-      <c r="B51" s="28">
+      <c r="B51" s="17">
         <v>39</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="G51" s="29"/>
-      <c r="H51" s="12" t="s">
+      <c r="G51" s="13"/>
+      <c r="H51" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="I51" s="15"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="12" t="s">
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="11" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:11">
-      <c r="A52" s="27">
+      <c r="A52" s="17">
         <v>39.1</v>
       </c>
-      <c r="B52" s="28" t="s">
+      <c r="B52" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="E52" s="12"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="14" t="s">
+      <c r="E52" s="11"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="I52" s="15"/>
-      <c r="J52" s="16"/>
-      <c r="K52" s="12"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="11"/>
     </row>
     <row r="53" customHeight="1" spans="1:11">
       <c r="A53" s="10">
         <v>40</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>40</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="H53" s="19"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="16" t="s">
+      <c r="H53" s="11"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="K53" s="12"/>
+      <c r="K53" s="11"/>
     </row>
     <row r="54" customHeight="1" spans="1:11">
-      <c r="A54" s="27">
+      <c r="A54" s="17">
         <v>41</v>
       </c>
-      <c r="B54" s="28">
+      <c r="B54" s="17">
         <v>41</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F54" s="13" t="s">
+      <c r="F54" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="G54" s="31"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="16"/>
-      <c r="K54" s="12" t="s">
+      <c r="G54" s="13"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:11">
-      <c r="A55" s="27">
+      <c r="A55" s="17">
         <v>41.1</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F55" s="13" t="s">
+      <c r="F55" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G55" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="H55" s="12" t="s">
+      <c r="H55" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="I55" s="15"/>
-      <c r="J55" s="16" t="s">
+      <c r="I55" s="14"/>
+      <c r="J55" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="K55" s="12"/>
+      <c r="K55" s="11"/>
     </row>
     <row r="56" customHeight="1" spans="1:11">
-      <c r="A56" s="27">
+      <c r="A56" s="17">
         <v>42</v>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="17">
         <v>42</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F56" s="41" t="s">
+      <c r="F56" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="G56" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="I56" s="15"/>
-      <c r="J56" s="16"/>
-      <c r="K56" s="12"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="11"/>
     </row>
     <row r="57" customHeight="1" spans="1:11">
-      <c r="A57" s="27">
+      <c r="A57" s="17">
         <v>43</v>
       </c>
-      <c r="B57" s="28">
+      <c r="B57" s="17">
         <v>43</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F57" s="13" t="s">
+      <c r="F57" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="G57" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H57" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="I57" s="15"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="23"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="11"/>
     </row>
     <row r="58" customHeight="1" spans="1:11">
-      <c r="A58" s="27">
+      <c r="A58" s="17">
         <v>44</v>
       </c>
-      <c r="B58" s="28">
+      <c r="B58" s="17">
         <v>44</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="E58" s="12" t="s">
+      <c r="E58" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="F58" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="G58" s="14" t="s">
+      <c r="G58" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="H58" s="12" t="s">
+      <c r="H58" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="I58" s="15"/>
-      <c r="J58" s="16"/>
-      <c r="K58" s="12" t="s">
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="11" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:11">
-      <c r="A59" s="27">
+      <c r="A59" s="17">
         <v>45</v>
       </c>
-      <c r="B59" s="28">
+      <c r="B59" s="17">
         <v>45</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="12" t="s">
         <v>342</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="G59" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="H59" s="12" t="s">
+      <c r="H59" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="I59" s="15"/>
-      <c r="J59" s="16"/>
-      <c r="K59" s="12" t="s">
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:11">
-      <c r="A60" s="27">
+      <c r="A60" s="17">
         <v>46</v>
       </c>
-      <c r="B60" s="28">
+      <c r="B60" s="17">
         <v>46</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="E60" s="12"/>
-      <c r="F60" s="13" t="s">
+      <c r="E60" s="11"/>
+      <c r="F60" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="G60" s="25" t="s">
+      <c r="G60" s="13" t="s">
         <v>348</v>
       </c>
-      <c r="H60" s="12" t="s">
+      <c r="H60" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="I60" s="15"/>
-      <c r="J60" s="16"/>
-      <c r="K60" s="12" t="s">
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="11" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:11">
-      <c r="A61" s="27">
+      <c r="A61" s="17">
         <v>46.1</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E61" s="12"/>
-      <c r="F61" s="41" t="s">
+      <c r="E61" s="11"/>
+      <c r="F61" s="25" t="s">
         <v>354</v>
       </c>
-      <c r="G61" s="14" t="s">
+      <c r="G61" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="H61" s="16" t="s">
+      <c r="H61" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="I61" s="15"/>
-      <c r="J61" s="16"/>
-      <c r="K61" s="12" t="s">
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="11" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:11">
-      <c r="A62" s="27">
+      <c r="A62" s="17">
         <v>47</v>
       </c>
-      <c r="B62" s="28">
+      <c r="B62" s="17">
         <v>47</v>
       </c>
-      <c r="C62" s="12" t="s">
+      <c r="C62" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="F62" s="13" t="s">
+      <c r="F62" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="G62" s="14" t="s">
+      <c r="G62" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="H62" s="12" t="s">
+      <c r="H62" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="I62" s="15"/>
-      <c r="J62" s="16"/>
-      <c r="K62" s="12" t="s">
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="11" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:11">
-      <c r="A63" s="27">
+      <c r="A63" s="17">
         <v>48</v>
       </c>
-      <c r="B63" s="28">
+      <c r="B63" s="17">
         <v>48</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F63" s="13" t="s">
+      <c r="F63" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="G63" s="14" t="s">
+      <c r="G63" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="H63" s="12" t="s">
+      <c r="H63" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="I63" s="15"/>
-      <c r="J63" s="16"/>
-      <c r="K63" s="12" t="s">
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:11">
-      <c r="A64" s="27">
+      <c r="A64" s="17">
         <v>49</v>
       </c>
-      <c r="B64" s="28">
+      <c r="B64" s="17">
         <v>49</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="F64" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="G64" s="14" t="s">
+      <c r="G64" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="H64" s="19"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="12"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="11"/>
     </row>
     <row r="65" customHeight="1" spans="1:11">
-      <c r="A65" s="27">
+      <c r="A65" s="17">
         <v>50</v>
       </c>
-      <c r="B65" s="28">
+      <c r="B65" s="17">
         <v>50</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F65" s="41" t="s">
+      <c r="F65" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="G65" s="29"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="16"/>
-      <c r="K65" s="12" t="s">
+      <c r="G65" s="13"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="14"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="11" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:11">
-      <c r="A66" s="27">
+      <c r="A66" s="17">
         <v>50.1</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="B66" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="E66" s="12"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="14" t="s">
+      <c r="E66" s="11"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="18" t="s">
         <v>380</v>
       </c>
-      <c r="H66" s="12" t="s">
+      <c r="H66" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="I66" s="15"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="12" t="s">
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="11" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:11">
-      <c r="A67" s="27">
+      <c r="A67" s="17">
         <v>51</v>
       </c>
-      <c r="B67" s="28">
+      <c r="B67" s="17">
         <v>51</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F67" s="41" t="s">
+      <c r="F67" s="25" t="s">
         <v>385</v>
       </c>
-      <c r="G67" s="29"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="16"/>
-      <c r="K67" s="12" t="s">
+      <c r="G67" s="13"/>
+      <c r="H67" s="11"/>
+      <c r="I67" s="14"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:11">
-      <c r="A68" s="27">
+      <c r="A68" s="17">
         <v>52</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="17">
         <v>52</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F68" s="41" t="s">
+      <c r="F68" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="G68" s="29"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="16"/>
-      <c r="K68" s="23" t="s">
+      <c r="G68" s="13"/>
+      <c r="H68" s="11"/>
+      <c r="I68" s="14"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="11" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:11">
-      <c r="A69" s="27">
+      <c r="A69" s="17">
         <v>53</v>
       </c>
-      <c r="B69" s="28">
+      <c r="B69" s="17">
         <v>53</v>
       </c>
-      <c r="C69" s="12" t="s">
+      <c r="C69" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F69" s="41" t="s">
+      <c r="F69" s="25" t="s">
         <v>391</v>
       </c>
-      <c r="G69" s="14" t="s">
+      <c r="G69" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="H69" s="12" t="s">
+      <c r="H69" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="I69" s="15"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="12" t="s">
+      <c r="I69" s="14"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:11">
-      <c r="A70" s="27">
+      <c r="A70" s="17">
         <v>54</v>
       </c>
-      <c r="B70" s="28">
+      <c r="B70" s="17">
         <v>54</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F70" s="13" t="s">
+      <c r="F70" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="G70" s="14" t="s">
+      <c r="G70" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="I70" s="15"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="21"/>
+      <c r="I70" s="14"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="15"/>
     </row>
     <row r="71" customHeight="1" spans="1:11">
-      <c r="A71" s="27">
+      <c r="A71" s="17">
         <v>55</v>
       </c>
-      <c r="B71" s="28">
+      <c r="B71" s="17">
         <v>55</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F71" s="13" t="s">
+      <c r="F71" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="G71" s="29"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="16"/>
-      <c r="K71" s="12" t="s">
+      <c r="G71" s="13"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="14"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="11" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:11">
-      <c r="A72" s="27">
+      <c r="A72" s="17">
         <v>56</v>
       </c>
-      <c r="B72" s="28">
+      <c r="B72" s="17">
         <v>56</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D72" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="F72" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="G72" s="14" t="s">
+      <c r="G72" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="H72" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="I72" s="15"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="12" t="s">
+      <c r="I72" s="14"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="11" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:11">
-      <c r="A73" s="27">
+      <c r="A73" s="17">
         <v>57</v>
       </c>
-      <c r="B73" s="28">
+      <c r="B73" s="17">
         <v>57</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="D73" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="F73" s="13" t="s">
+      <c r="F73" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" s="13" t="s">
         <v>413</v>
       </c>
-      <c r="H73" s="19"/>
-      <c r="I73" s="15"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="12"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="14"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="11"/>
     </row>
     <row r="74" customHeight="1" spans="1:11">
-      <c r="A74" s="27">
+      <c r="A74" s="17">
         <v>58</v>
       </c>
-      <c r="B74" s="28">
+      <c r="B74" s="17">
         <v>58</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E74" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="F74" s="13" t="s">
+      <c r="F74" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="G74" s="14" t="s">
+      <c r="G74" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="I74" s="15"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="12" t="s">
+      <c r="I74" s="14"/>
+      <c r="J74" s="14"/>
+      <c r="K74" s="11" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:11">
-      <c r="A75" s="27">
+      <c r="A75" s="17">
         <v>58.1</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="E75" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F75" s="41" t="s">
+      <c r="F75" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="G75" s="14" t="s">
+      <c r="G75" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="I75" s="15"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="23" t="s">
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="11" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:11">
-      <c r="A76" s="27">
+      <c r="A76" s="17">
         <v>59</v>
       </c>
-      <c r="B76" s="28">
+      <c r="B76" s="17">
         <v>59</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="G76" s="14" t="s">
+      <c r="G76" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="H76" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="I76" s="15"/>
-      <c r="J76" s="16"/>
-      <c r="K76" s="12" t="s">
+      <c r="I76" s="14"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="11" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:11">
-      <c r="A77" s="27">
+      <c r="A77" s="17">
         <v>60</v>
       </c>
-      <c r="B77" s="28">
+      <c r="B77" s="17">
         <v>60</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="12" t="s">
         <v>436</v>
       </c>
-      <c r="G77" s="14" t="s">
+      <c r="G77" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="H77" s="12" t="s">
+      <c r="H77" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="I77" s="15"/>
-      <c r="J77" s="16" t="s">
+      <c r="I77" s="14"/>
+      <c r="J77" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="K77" s="12"/>
+      <c r="K77" s="11"/>
     </row>
     <row r="78" customHeight="1" spans="1:11">
-      <c r="A78" s="32"/>
-      <c r="B78" s="28"/>
-      <c r="C78" s="12" t="s">
+      <c r="A78" s="19"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="E78" s="12"/>
-      <c r="F78" s="42" t="s">
+      <c r="E78" s="11"/>
+      <c r="F78" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="G78" s="29"/>
-      <c r="H78" s="12" t="s">
+      <c r="G78" s="13"/>
+      <c r="H78" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="I78" s="15"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="12" t="s">
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="11" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:11">
-      <c r="A79" s="32"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="12" t="s">
+      <c r="A79" s="19"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F79" s="22" t="s">
+      <c r="F79" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="G79" s="26" t="s">
+      <c r="G79" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="H79" s="12" t="s">
+      <c r="H79" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I79" s="23" t="s">
+      <c r="I79" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J79" s="16"/>
-      <c r="K79" s="23"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="11"/>
     </row>
     <row r="80" customHeight="1" spans="1:11">
-      <c r="A80" s="32"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="12" t="s">
+      <c r="A80" s="19"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F80" s="22" t="s">
+      <c r="F80" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="G80" s="29"/>
-      <c r="H80" s="12"/>
-      <c r="I80" s="15" t="s">
+      <c r="G80" s="13"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J80" s="16"/>
-      <c r="K80" s="12" t="s">
+      <c r="J80" s="14"/>
+      <c r="K80" s="11" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:11">
-      <c r="A81" s="32"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="12" t="s">
+      <c r="A81" s="19"/>
+      <c r="B81" s="17"/>
+      <c r="C81" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="E81" s="12" t="s">
+      <c r="E81" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F81" s="13" t="s">
+      <c r="F81" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="G81" s="29"/>
-      <c r="H81" s="12" t="s">
+      <c r="G81" s="13"/>
+      <c r="H81" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I81" s="23" t="s">
+      <c r="I81" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J81" s="16"/>
-      <c r="K81" s="23"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="11"/>
     </row>
     <row r="82" customHeight="1" spans="1:11">
-      <c r="A82" s="32"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="12" t="s">
+      <c r="A82" s="19"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="E82" s="12" t="s">
+      <c r="E82" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F82" s="22" t="s">
+      <c r="F82" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="G82" s="29"/>
-      <c r="H82" s="12" t="s">
+      <c r="G82" s="13"/>
+      <c r="H82" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="I82" s="23" t="s">
+      <c r="I82" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="J82" s="16"/>
-      <c r="K82" s="23"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="11"/>
     </row>
     <row r="83" customHeight="1" spans="1:11">
-      <c r="A83" s="32"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="12" t="s">
+      <c r="A83" s="19"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="E83" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F83" s="42" t="s">
+      <c r="F83" s="25" t="s">
         <v>462</v>
       </c>
-      <c r="G83" s="29"/>
-      <c r="H83" s="12" t="s">
+      <c r="G83" s="13"/>
+      <c r="H83" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I83" s="17"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="17"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="11"/>
     </row>
     <row r="84" customHeight="1" spans="1:11">
-      <c r="A84" s="32"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="12" t="s">
+      <c r="A84" s="19"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F84" s="42" t="s">
+      <c r="F84" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="G84" s="31"/>
-      <c r="H84" s="12" t="s">
+      <c r="G84" s="13"/>
+      <c r="H84" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I84" s="17"/>
-      <c r="J84" s="18"/>
-      <c r="K84" s="17"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="11"/>
     </row>
     <row r="85" customHeight="1" spans="1:11">
-      <c r="A85" s="32"/>
-      <c r="B85" s="28"/>
-      <c r="C85" s="12" t="s">
+      <c r="A85" s="19"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="41" t="s">
+      <c r="F85" s="25" t="s">
         <v>468</v>
       </c>
-      <c r="G85" s="14" t="s">
+      <c r="G85" s="13" t="s">
         <v>469</v>
       </c>
-      <c r="H85" s="12" t="s">
+      <c r="H85" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I85" s="15"/>
-      <c r="J85" s="16" t="s">
+      <c r="I85" s="14"/>
+      <c r="J85" s="14" t="s">
         <v>470</v>
       </c>
-      <c r="K85" s="23"/>
+      <c r="K85" s="11"/>
     </row>
     <row r="86" customHeight="1" spans="1:11">
-      <c r="A86" s="32"/>
-      <c r="B86" s="28"/>
-      <c r="C86" s="12" t="s">
+      <c r="A86" s="19"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="41" t="s">
+      <c r="F86" s="25" t="s">
         <v>468</v>
       </c>
-      <c r="G86" s="29"/>
-      <c r="H86" s="12" t="s">
+      <c r="G86" s="13"/>
+      <c r="H86" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I86" s="21"/>
-      <c r="J86" s="16" t="s">
+      <c r="I86" s="15"/>
+      <c r="J86" s="14" t="s">
         <v>473</v>
       </c>
-      <c r="K86" s="23"/>
+      <c r="K86" s="11"/>
     </row>
     <row r="87" customHeight="1" spans="1:11">
-      <c r="A87" s="32"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="12" t="s">
+      <c r="A87" s="19"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="41" t="s">
+      <c r="F87" s="25" t="s">
         <v>468</v>
       </c>
-      <c r="G87" s="29"/>
-      <c r="H87" s="12" t="s">
+      <c r="G87" s="13"/>
+      <c r="H87" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I87" s="23" t="s">
+      <c r="I87" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="J87" s="16"/>
-      <c r="K87" s="23"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="11"/>
     </row>
     <row r="88" customHeight="1" spans="1:11">
-      <c r="A88" s="32"/>
-      <c r="B88" s="28"/>
-      <c r="C88" s="12" t="s">
+      <c r="A88" s="19"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E88" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="41" t="s">
+      <c r="F88" s="25" t="s">
         <v>468</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="G88" s="13" t="s">
         <v>479</v>
       </c>
-      <c r="H88" s="12" t="s">
+      <c r="H88" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I88" s="17"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="17"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="11"/>
     </row>
     <row r="89" customHeight="1" spans="1:11">
-      <c r="A89" s="32"/>
-      <c r="B89" s="28"/>
-      <c r="C89" s="12" t="s">
+      <c r="A89" s="19"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E89" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F89" s="13" t="s">
+      <c r="F89" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="G89" s="29"/>
-      <c r="H89" s="12" t="s">
+      <c r="G89" s="13"/>
+      <c r="H89" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I89" s="12" t="s">
+      <c r="I89" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="J89" s="16"/>
-      <c r="K89" s="23"/>
+      <c r="J89" s="14"/>
+      <c r="K89" s="11"/>
     </row>
     <row r="90" customHeight="1" spans="1:11">
-      <c r="A90" s="32"/>
-      <c r="B90" s="28"/>
-      <c r="C90" s="12" t="s">
+      <c r="A90" s="19"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="E90" s="12" t="s">
+      <c r="E90" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F90" s="13" t="s">
+      <c r="F90" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="G90" s="14" t="s">
+      <c r="G90" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="H90" s="12" t="s">
+      <c r="H90" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I90" s="17"/>
-      <c r="J90" s="18"/>
-      <c r="K90" s="17"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="14"/>
+      <c r="K90" s="11"/>
     </row>
     <row r="91" customHeight="1" spans="1:11">
-      <c r="A91" s="32"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="12" t="s">
+      <c r="A91" s="19"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="E91" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F91" s="13" t="s">
+      <c r="F91" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="G91" s="14" t="s">
+      <c r="G91" s="13" t="s">
         <v>489</v>
       </c>
-      <c r="H91" s="12" t="s">
+      <c r="H91" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I91" s="17"/>
-      <c r="J91" s="18"/>
-      <c r="K91" s="19"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="14"/>
+      <c r="K91" s="11"/>
     </row>
     <row r="92" customHeight="1" spans="1:11">
-      <c r="A92" s="32"/>
-      <c r="B92" s="28"/>
-      <c r="C92" s="12" t="s">
+      <c r="A92" s="19"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="E92" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F92" s="22" t="s">
+      <c r="F92" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="G92" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="H92" s="21"/>
-      <c r="I92" s="23" t="s">
+      <c r="H92" s="15"/>
+      <c r="I92" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="J92" s="16"/>
-      <c r="K92" s="12" t="s">
+      <c r="J92" s="14"/>
+      <c r="K92" s="11" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:11">
-      <c r="A93" s="32"/>
-      <c r="B93" s="28"/>
-      <c r="C93" s="12" t="s">
+      <c r="A93" s="19"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="E93" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F93" s="13" t="s">
+      <c r="F93" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="G93" s="29"/>
-      <c r="H93" s="12" t="s">
+      <c r="G93" s="13"/>
+      <c r="H93" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="I93" s="12" t="s">
+      <c r="I93" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="J93" s="16"/>
-      <c r="K93" s="12"/>
+      <c r="J93" s="14"/>
+      <c r="K93" s="11"/>
     </row>
     <row r="94" customHeight="1" spans="1:11">
-      <c r="A94" s="32"/>
-      <c r="B94" s="28"/>
-      <c r="C94" s="12" t="s">
+      <c r="A94" s="19"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="E94" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F94" s="22" t="s">
+      <c r="F94" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="G94" s="14" t="s">
+      <c r="G94" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="H94" s="19"/>
-      <c r="I94" s="12" t="s">
+      <c r="H94" s="11"/>
+      <c r="I94" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="J94" s="16"/>
-      <c r="K94" s="12"/>
+      <c r="J94" s="14"/>
+      <c r="K94" s="11"/>
     </row>
     <row r="95" customHeight="1" spans="1:11">
-      <c r="A95" s="32"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="12" t="s">
+      <c r="A95" s="19"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E95" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F95" s="13" t="s">
+      <c r="F95" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G95" s="14" t="s">
+      <c r="G95" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="H95" s="12" t="s">
+      <c r="H95" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="I95" s="12" t="s">
+      <c r="I95" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="J95" s="16"/>
-      <c r="K95" s="12" t="s">
+      <c r="J95" s="14"/>
+      <c r="K95" s="11" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:11">
-      <c r="A96" s="32"/>
-      <c r="B96" s="28"/>
-      <c r="C96" s="12" t="s">
+      <c r="A96" s="19"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E96" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="22" t="s">
+      <c r="F96" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G96" s="29"/>
-      <c r="H96" s="12" t="s">
+      <c r="G96" s="13"/>
+      <c r="H96" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="I96" s="21"/>
-      <c r="J96" s="16"/>
-      <c r="K96" s="12" t="s">
+      <c r="I96" s="15"/>
+      <c r="J96" s="14"/>
+      <c r="K96" s="11" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:11">
       <c r="A97" s="10"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="12" t="s">
+      <c r="B97" s="10"/>
+      <c r="C97" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="E97" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F97" s="13" t="s">
+      <c r="F97" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G97" s="14" t="s">
+      <c r="G97" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="H97" s="12" t="s">
+      <c r="H97" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="I97" s="16" t="s">
+      <c r="I97" s="14" t="s">
         <v>505</v>
       </c>
-      <c r="J97" s="16"/>
-      <c r="K97" s="12" t="s">
+      <c r="J97" s="14"/>
+      <c r="K97" s="11" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:11">
       <c r="A98" s="10"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="12" t="s">
+      <c r="B98" s="10"/>
+      <c r="C98" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="E98" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F98" s="13" t="s">
+      <c r="F98" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G98" s="14" t="s">
+      <c r="G98" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="H98" s="12" t="s">
+      <c r="H98" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="I98" s="23" t="s">
+      <c r="I98" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="J98" s="16"/>
-      <c r="K98" s="12" t="s">
+      <c r="J98" s="14"/>
+      <c r="K98" s="11" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:11">
-      <c r="A99" s="32"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="12" t="s">
+      <c r="A99" s="19"/>
+      <c r="B99" s="17"/>
+      <c r="C99" s="11" t="s">
         <v>521</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="E99" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F99" s="13" t="s">
+      <c r="F99" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G99" s="14" t="s">
+      <c r="G99" s="13" t="s">
         <v>523</v>
       </c>
-      <c r="H99" s="12" t="s">
+      <c r="H99" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="I99" s="21"/>
-      <c r="J99" s="16"/>
-      <c r="K99" s="12" t="s">
+      <c r="I99" s="15"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="11" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:11">
-      <c r="A100" s="32"/>
-      <c r="B100" s="28"/>
-      <c r="C100" s="12" t="s">
+      <c r="A100" s="19"/>
+      <c r="B100" s="17"/>
+      <c r="C100" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="E100" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F100" s="13" t="s">
+      <c r="F100" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G100" s="26" t="s">
+      <c r="G100" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="H100" s="12" t="s">
+      <c r="H100" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="I100" s="15" t="s">
+      <c r="I100" s="14" t="s">
         <v>505</v>
       </c>
-      <c r="J100" s="16"/>
-      <c r="K100" s="12" t="s">
+      <c r="J100" s="14"/>
+      <c r="K100" s="11" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:11">
-      <c r="A101" s="32"/>
-      <c r="B101" s="28"/>
-      <c r="C101" s="12" t="s">
+      <c r="A101" s="19"/>
+      <c r="B101" s="17"/>
+      <c r="C101" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="E101" s="12" t="s">
+      <c r="E101" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F101" s="13" t="s">
+      <c r="F101" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G101" s="29"/>
-      <c r="H101" s="12" t="s">
+      <c r="G101" s="13"/>
+      <c r="H101" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="I101" s="23" t="s">
+      <c r="I101" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="J101" s="16"/>
-      <c r="K101" s="12"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="11"/>
     </row>
     <row r="102" customHeight="1" spans="1:11">
-      <c r="A102" s="32"/>
-      <c r="B102" s="28"/>
-      <c r="C102" s="12" t="s">
+      <c r="A102" s="19"/>
+      <c r="B102" s="17"/>
+      <c r="C102" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="E102" s="12" t="s">
+      <c r="E102" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F102" s="13" t="s">
+      <c r="F102" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="G102" s="14" t="s">
+      <c r="G102" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="H102" s="12" t="s">
+      <c r="H102" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I102" s="23" t="s">
+      <c r="I102" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="J102" s="16"/>
-      <c r="K102" s="12"/>
+      <c r="J102" s="14"/>
+      <c r="K102" s="11"/>
     </row>
     <row r="103" customHeight="1" spans="1:11">
-      <c r="A103" s="32"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="12" t="s">
+      <c r="A103" s="19"/>
+      <c r="B103" s="17"/>
+      <c r="C103" s="11" t="s">
         <v>536</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="E103" s="12" t="s">
+      <c r="E103" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F103" s="13" t="s">
+      <c r="F103" s="12" t="s">
         <v>538</v>
       </c>
-      <c r="G103" s="14" t="s">
+      <c r="G103" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="H103" s="12" t="s">
+      <c r="H103" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I103" s="17"/>
-      <c r="J103" s="18"/>
-      <c r="K103" s="19"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="11"/>
     </row>
     <row r="104" customHeight="1" spans="1:11">
-      <c r="A104" s="32"/>
-      <c r="B104" s="28"/>
-      <c r="C104" s="12" t="s">
+      <c r="A104" s="19"/>
+      <c r="B104" s="17"/>
+      <c r="C104" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F104" s="13" t="s">
+      <c r="F104" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="G104" s="29"/>
-      <c r="H104" s="21"/>
-      <c r="I104" s="12" t="s">
+      <c r="G104" s="13"/>
+      <c r="H104" s="15"/>
+      <c r="I104" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J104" s="16"/>
-      <c r="K104" s="12" t="s">
+      <c r="J104" s="14"/>
+      <c r="K104" s="11" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:11">
-      <c r="A105" s="32"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="12" t="s">
+      <c r="A105" s="19"/>
+      <c r="B105" s="17"/>
+      <c r="C105" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="D105" s="12" t="s">
+      <c r="D105" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E105" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F105" s="13" t="s">
+      <c r="F105" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="G105" s="18" t="s">
         <v>546</v>
       </c>
-      <c r="H105" s="12" t="s">
+      <c r="H105" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I105" s="17"/>
-      <c r="J105" s="18"/>
-      <c r="K105" s="19"/>
+      <c r="I105" s="11"/>
+      <c r="J105" s="14"/>
+      <c r="K105" s="11"/>
     </row>
     <row r="106" customHeight="1" spans="1:11">
-      <c r="A106" s="32"/>
-      <c r="B106" s="28"/>
-      <c r="C106" s="12" t="s">
+      <c r="A106" s="19"/>
+      <c r="B106" s="17"/>
+      <c r="C106" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="D106" s="12" t="s">
+      <c r="D106" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="E106" s="12" t="s">
+      <c r="E106" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F106" s="13" t="s">
+      <c r="F106" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G106" s="33" t="s">
+      <c r="G106" s="13" t="s">
         <v>549</v>
       </c>
-      <c r="H106" s="19"/>
-      <c r="I106" s="17"/>
-      <c r="J106" s="18"/>
-      <c r="K106" s="17"/>
+      <c r="H106" s="11"/>
+      <c r="I106" s="11"/>
+      <c r="J106" s="14"/>
+      <c r="K106" s="11"/>
     </row>
     <row r="107" customHeight="1" spans="1:11">
-      <c r="A107" s="32"/>
-      <c r="B107" s="28"/>
-      <c r="C107" s="12" t="s">
+      <c r="A107" s="19"/>
+      <c r="B107" s="17"/>
+      <c r="C107" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E107" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="41" t="s">
+      <c r="F107" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="G107" s="14" t="s">
+      <c r="G107" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="H107" s="19"/>
-      <c r="I107" s="23" t="s">
+      <c r="H107" s="11"/>
+      <c r="I107" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="J107" s="16"/>
-      <c r="K107" s="23"/>
+      <c r="J107" s="14"/>
+      <c r="K107" s="11"/>
     </row>
     <row r="108" customHeight="1" spans="1:11">
-      <c r="A108" s="32"/>
-      <c r="B108" s="28"/>
-      <c r="C108" s="12" t="s">
+      <c r="A108" s="19"/>
+      <c r="B108" s="17"/>
+      <c r="C108" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="D108" s="12" t="s">
+      <c r="D108" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="E108" s="12" t="s">
+      <c r="E108" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F108" s="13" t="s">
+      <c r="F108" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="G108" s="29"/>
-      <c r="H108" s="19"/>
-      <c r="I108" s="15" t="s">
+      <c r="G108" s="13"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J108" s="16" t="s">
+      <c r="J108" s="14" t="s">
         <v>557</v>
       </c>
-      <c r="K108" s="12"/>
+      <c r="K108" s="11"/>
     </row>
     <row r="109" customHeight="1" spans="1:11">
-      <c r="A109" s="32"/>
-      <c r="B109" s="28"/>
-      <c r="C109" s="12" t="s">
+      <c r="A109" s="19"/>
+      <c r="B109" s="17"/>
+      <c r="C109" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="D109" s="12" t="s">
+      <c r="D109" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="E109" s="12" t="s">
+      <c r="E109" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="13" t="s">
+      <c r="F109" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="G109" s="29"/>
-      <c r="H109" s="19"/>
-      <c r="I109" s="23" t="s">
+      <c r="G109" s="13"/>
+      <c r="H109" s="11"/>
+      <c r="I109" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J109" s="16"/>
-      <c r="K109" s="12"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="11"/>
     </row>
     <row r="110" customHeight="1" spans="1:11">
-      <c r="A110" s="32"/>
-      <c r="B110" s="28"/>
-      <c r="C110" s="12" t="s">
+      <c r="A110" s="19"/>
+      <c r="B110" s="17"/>
+      <c r="C110" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D110" s="12" t="s">
+      <c r="D110" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="E110" s="12" t="s">
+      <c r="E110" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F110" s="13" t="s">
+      <c r="F110" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="G110" s="29"/>
-      <c r="H110" s="12" t="s">
+      <c r="G110" s="13"/>
+      <c r="H110" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="I110" s="23" t="s">
+      <c r="I110" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J110" s="16"/>
-      <c r="K110" s="23"/>
+      <c r="J110" s="14"/>
+      <c r="K110" s="11"/>
     </row>
     <row r="111" customHeight="1" spans="1:11">
-      <c r="A111" s="32"/>
-      <c r="B111" s="28"/>
-      <c r="C111" s="12" t="s">
+      <c r="A111" s="19"/>
+      <c r="B111" s="17"/>
+      <c r="C111" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="D111" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="E111" s="12" t="s">
+      <c r="E111" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F111" s="41" t="s">
+      <c r="F111" s="25" t="s">
         <v>565</v>
       </c>
-      <c r="G111" s="14" t="s">
+      <c r="G111" s="13" t="s">
         <v>566</v>
       </c>
-      <c r="H111" s="12" t="s">
+      <c r="H111" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I111" s="21"/>
-      <c r="J111" s="16" t="s">
+      <c r="I111" s="15"/>
+      <c r="J111" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="K111" s="23"/>
+      <c r="K111" s="11"/>
     </row>
     <row r="112" customHeight="1" spans="1:11">
-      <c r="A112" s="32"/>
-      <c r="B112" s="28"/>
-      <c r="C112" s="12" t="s">
+      <c r="A112" s="19"/>
+      <c r="B112" s="17"/>
+      <c r="C112" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="D112" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="E112" s="12"/>
-      <c r="F112" s="13" t="s">
+      <c r="E112" s="11"/>
+      <c r="F112" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="G112" s="14" t="s">
+      <c r="G112" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="H112" s="12" t="s">
+      <c r="H112" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="I112" s="16" t="s">
+      <c r="I112" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J112" s="16"/>
-      <c r="K112" s="12" t="s">
+      <c r="J112" s="14"/>
+      <c r="K112" s="11" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:11">
-      <c r="A113" s="32"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="12" t="s">
+      <c r="A113" s="19"/>
+      <c r="B113" s="17"/>
+      <c r="C113" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="E113" s="12" t="s">
+      <c r="E113" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F113" s="41" t="s">
+      <c r="F113" s="25" t="s">
         <v>576</v>
       </c>
-      <c r="G113" s="29"/>
-      <c r="H113" s="19"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="16"/>
-      <c r="K113" s="23" t="s">
+      <c r="G113" s="13"/>
+      <c r="H113" s="11"/>
+      <c r="I113" s="15"/>
+      <c r="J113" s="14"/>
+      <c r="K113" s="11" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:11">
-      <c r="A114" s="32"/>
-      <c r="B114" s="28"/>
-      <c r="C114" s="12" t="s">
+      <c r="A114" s="19"/>
+      <c r="B114" s="17"/>
+      <c r="C114" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="D114" s="12" t="s">
+      <c r="D114" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E114" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F114" s="13" t="s">
+      <c r="F114" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="G114" s="29"/>
-      <c r="H114" s="12" t="s">
+      <c r="G114" s="13"/>
+      <c r="H114" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="I114" s="15"/>
-      <c r="J114" s="16"/>
-      <c r="K114" s="12" t="s">
+      <c r="I114" s="14"/>
+      <c r="J114" s="14"/>
+      <c r="K114" s="11" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:11">
-      <c r="A115" s="32"/>
-      <c r="B115" s="28"/>
-      <c r="C115" s="12" t="s">
+      <c r="A115" s="19"/>
+      <c r="B115" s="17"/>
+      <c r="C115" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="D115" s="12" t="s">
+      <c r="D115" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F115" s="13" t="s">
+      <c r="F115" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="G115" s="29"/>
-      <c r="H115" s="12" t="s">
+      <c r="G115" s="13"/>
+      <c r="H115" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="I115" s="21"/>
-      <c r="J115" s="16"/>
-      <c r="K115" s="12" t="s">
+      <c r="I115" s="15"/>
+      <c r="J115" s="14"/>
+      <c r="K115" s="11" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:11">
-      <c r="A116" s="32"/>
-      <c r="B116" s="28"/>
-      <c r="C116" s="12" t="s">
+      <c r="A116" s="19"/>
+      <c r="B116" s="17"/>
+      <c r="C116" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="D116" s="12" t="s">
+      <c r="D116" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="E116" s="12"/>
-      <c r="F116" s="13" t="s">
+      <c r="E116" s="11"/>
+      <c r="F116" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="G116" s="31"/>
-      <c r="H116" s="12" t="s">
+      <c r="G116" s="13"/>
+      <c r="H116" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="I116" s="15"/>
-      <c r="J116" s="16"/>
-      <c r="K116" s="12" t="s">
+      <c r="I116" s="14"/>
+      <c r="J116" s="14"/>
+      <c r="K116" s="11" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:11">
-      <c r="A117" s="32"/>
-      <c r="B117" s="28"/>
-      <c r="C117" s="12" t="s">
+      <c r="A117" s="19"/>
+      <c r="B117" s="17"/>
+      <c r="C117" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="D117" s="12" t="s">
+      <c r="D117" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="E117" s="12" t="s">
+      <c r="E117" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="F117" s="13" t="s">
+      <c r="F117" s="12" t="s">
         <v>596</v>
       </c>
-      <c r="G117" s="14" t="s">
+      <c r="G117" s="13" t="s">
         <v>597</v>
       </c>
-      <c r="H117" s="19"/>
-      <c r="I117" s="21"/>
-      <c r="J117" s="16" t="s">
+      <c r="H117" s="11"/>
+      <c r="I117" s="15"/>
+      <c r="J117" s="14" t="s">
         <v>598</v>
       </c>
-      <c r="K117" s="23"/>
+      <c r="K117" s="11"/>
     </row>
     <row r="118" customHeight="1" spans="1:11">
-      <c r="A118" s="32"/>
-      <c r="B118" s="28"/>
-      <c r="C118" s="12" t="s">
+      <c r="A118" s="19"/>
+      <c r="B118" s="17"/>
+      <c r="C118" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D118" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="E118" s="12" t="s">
+      <c r="E118" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F118" s="42" t="s">
+      <c r="F118" s="25" t="s">
         <v>601</v>
       </c>
-      <c r="G118" s="14" t="s">
+      <c r="G118" s="13" t="s">
         <v>602</v>
       </c>
-      <c r="H118" s="12" t="s">
+      <c r="H118" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="I118" s="21"/>
-      <c r="J118" s="16" t="s">
+      <c r="I118" s="15"/>
+      <c r="J118" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="K118" s="12"/>
+      <c r="K118" s="11"/>
     </row>
     <row r="119" customHeight="1" spans="1:11">
-      <c r="A119" s="32"/>
-      <c r="B119" s="28"/>
-      <c r="C119" s="12" t="s">
+      <c r="A119" s="19"/>
+      <c r="B119" s="17"/>
+      <c r="C119" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="E119" s="12" t="s">
+      <c r="E119" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F119" s="42" t="s">
+      <c r="F119" s="25" t="s">
         <v>259</v>
       </c>
-      <c r="G119" s="29"/>
-      <c r="H119" s="19"/>
-      <c r="I119" s="15" t="s">
+      <c r="G119" s="13"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J119" s="16"/>
-      <c r="K119" s="23" t="s">
+      <c r="J119" s="14"/>
+      <c r="K119" s="11" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:11">
-      <c r="A120" s="32"/>
-      <c r="B120" s="28"/>
-      <c r="C120" s="12" t="s">
+      <c r="A120" s="19"/>
+      <c r="B120" s="17"/>
+      <c r="C120" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D120" s="12" t="s">
+      <c r="D120" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="E120" s="12"/>
-      <c r="F120" s="13" t="s">
+      <c r="E120" s="11"/>
+      <c r="F120" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="G120" s="33" t="s">
+      <c r="G120" s="13" t="s">
         <v>611</v>
       </c>
-      <c r="H120" s="23" t="s">
+      <c r="H120" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="I120" s="21"/>
-      <c r="J120" s="16"/>
-      <c r="K120" s="12" t="s">
+      <c r="I120" s="15"/>
+      <c r="J120" s="14"/>
+      <c r="K120" s="11" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:11">
-      <c r="A121" s="32"/>
-      <c r="B121" s="28"/>
-      <c r="C121" s="12" t="s">
+      <c r="A121" s="19"/>
+      <c r="B121" s="17"/>
+      <c r="C121" s="11" t="s">
         <v>614</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D121" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E121" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F121" s="13" t="s">
+      <c r="F121" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="G121" s="29"/>
-      <c r="H121" s="19"/>
-      <c r="I121" s="15"/>
-      <c r="J121" s="16"/>
-      <c r="K121" s="12" t="s">
+      <c r="G121" s="13"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="14"/>
+      <c r="J121" s="14"/>
+      <c r="K121" s="11" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:11">
-      <c r="A122" s="32"/>
-      <c r="B122" s="28"/>
-      <c r="C122" s="12" t="s">
+      <c r="A122" s="19"/>
+      <c r="B122" s="17"/>
+      <c r="C122" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="D122" s="12" t="s">
+      <c r="D122" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="E122" s="12" t="s">
+      <c r="E122" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F122" s="13" t="s">
+      <c r="F122" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="G122" s="14" t="s">
+      <c r="G122" s="13" t="s">
         <v>621</v>
       </c>
-      <c r="H122" s="12" t="s">
+      <c r="H122" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="I122" s="15" t="s">
+      <c r="I122" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J122" s="16"/>
-      <c r="K122" s="12" t="s">
+      <c r="J122" s="14"/>
+      <c r="K122" s="11" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:11">
-      <c r="A123" s="32"/>
-      <c r="B123" s="28"/>
-      <c r="C123" s="12" t="s">
+      <c r="A123" s="19"/>
+      <c r="B123" s="17"/>
+      <c r="C123" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="E123" s="12" t="s">
+      <c r="E123" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="F123" s="13" t="s">
+      <c r="F123" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="G123" s="14" t="s">
+      <c r="G123" s="18" t="s">
         <v>627</v>
       </c>
-      <c r="H123" s="12" t="s">
+      <c r="H123" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="I123" s="15" t="s">
+      <c r="I123" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J123" s="16"/>
-      <c r="K123" s="12" t="s">
+      <c r="J123" s="14"/>
+      <c r="K123" s="11" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:11">
-      <c r="A124" s="32"/>
-      <c r="B124" s="28"/>
-      <c r="C124" s="12" t="s">
+      <c r="A124" s="19"/>
+      <c r="B124" s="17"/>
+      <c r="C124" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="D124" s="12" t="s">
+      <c r="D124" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="E124" s="12"/>
-      <c r="F124" s="41" t="s">
+      <c r="E124" s="11"/>
+      <c r="F124" s="25" t="s">
         <v>632</v>
       </c>
-      <c r="G124" s="14" t="s">
+      <c r="H124" s="11"/>
+      <c r="I124" s="11" t="s">
         <v>633</v>
       </c>
-      <c r="H124" s="17"/>
-      <c r="I124" s="12" t="s">
+      <c r="J124" s="14"/>
+      <c r="K124" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="J124" s="16"/>
-      <c r="K124" s="12"/>
     </row>
     <row r="125" customHeight="1" spans="1:11">
-      <c r="A125" s="32"/>
-      <c r="B125" s="28"/>
-      <c r="C125" s="12" t="s">
+      <c r="A125" s="19"/>
+      <c r="B125" s="17"/>
+      <c r="C125" s="11" t="s">
         <v>635</v>
       </c>
-      <c r="D125" s="12" t="s">
+      <c r="D125" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="E125" s="12" t="s">
+      <c r="E125" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F125" s="41" t="s">
+      <c r="F125" s="25" t="s">
         <v>637</v>
       </c>
-      <c r="G125" s="14" t="s">
+      <c r="G125" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="H125" s="23" t="s">
+      <c r="H125" s="11" t="s">
         <v>639</v>
       </c>
-      <c r="I125" s="21"/>
-      <c r="J125" s="16"/>
-      <c r="K125" s="23" t="s">
+      <c r="I125" s="15"/>
+      <c r="J125" s="14"/>
+      <c r="K125" s="11" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:11">
-      <c r="A126" s="32"/>
-      <c r="B126" s="28"/>
-      <c r="C126" s="12" t="s">
+      <c r="A126" s="19"/>
+      <c r="B126" s="17"/>
+      <c r="C126" s="11" t="s">
         <v>641</v>
       </c>
-      <c r="D126" s="12" t="s">
+      <c r="D126" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="E126" s="12" t="s">
+      <c r="E126" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="F126" s="41" t="s">
+      <c r="F126" s="25" t="s">
         <v>644</v>
       </c>
-      <c r="G126" s="29"/>
-      <c r="H126" s="12" t="s">
+      <c r="G126" s="13"/>
+      <c r="H126" s="11" t="s">
         <v>639</v>
       </c>
-      <c r="I126" s="21"/>
-      <c r="J126" s="16"/>
-      <c r="K126" s="12" t="s">
+      <c r="I126" s="15"/>
+      <c r="J126" s="14"/>
+      <c r="K126" s="11" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:11">
-      <c r="A127" s="32"/>
-      <c r="B127" s="28"/>
-      <c r="C127" s="12" t="s">
+      <c r="A127" s="19"/>
+      <c r="B127" s="17"/>
+      <c r="C127" s="11" t="s">
         <v>646</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="11" t="s">
         <v>647</v>
       </c>
-      <c r="E127" s="12"/>
-      <c r="F127" s="13" t="s">
+      <c r="E127" s="11"/>
+      <c r="F127" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="G127" s="29"/>
-      <c r="H127" s="19"/>
-      <c r="I127" s="20"/>
-      <c r="J127" s="16"/>
-      <c r="K127" s="23" t="s">
+      <c r="G127" s="13"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="15"/>
+      <c r="J127" s="14"/>
+      <c r="K127" s="11" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:11">
-      <c r="A128" s="32"/>
-      <c r="B128" s="28"/>
-      <c r="C128" s="12" t="s">
+      <c r="A128" s="19"/>
+      <c r="B128" s="17"/>
+      <c r="C128" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="11" t="s">
         <v>650</v>
       </c>
-      <c r="E128" s="12" t="s">
+      <c r="E128" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F128" s="13" t="s">
+      <c r="F128" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G128" s="26" t="s">
+      <c r="G128" s="13" t="s">
         <v>652</v>
       </c>
-      <c r="H128" s="12" t="s">
+      <c r="H128" s="11" t="s">
         <v>653</v>
       </c>
-      <c r="I128" s="15"/>
-      <c r="J128" s="16"/>
-      <c r="K128" s="12" t="s">
+      <c r="I128" s="14"/>
+      <c r="J128" s="14"/>
+      <c r="K128" s="11" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:11">
-      <c r="A129" s="32"/>
-      <c r="B129" s="28"/>
-      <c r="C129" s="12" t="s">
+      <c r="A129" s="19"/>
+      <c r="B129" s="17"/>
+      <c r="C129" s="11" t="s">
         <v>655</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="11" t="s">
         <v>656</v>
       </c>
-      <c r="E129" s="12" t="s">
+      <c r="E129" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F129" s="13" t="s">
+      <c r="F129" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="G129" s="14" t="s">
+      <c r="G129" s="13" t="s">
         <v>658</v>
       </c>
-      <c r="H129" s="23" t="s">
+      <c r="H129" s="11" t="s">
         <v>659</v>
       </c>
-      <c r="I129" s="19"/>
-      <c r="J129" s="18"/>
-      <c r="K129" s="19"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="14"/>
+      <c r="K129" s="11"/>
     </row>
     <row r="130" customHeight="1" spans="1:11">
-      <c r="A130" s="32"/>
-      <c r="B130" s="28"/>
-      <c r="C130" s="12" t="s">
+      <c r="A130" s="19"/>
+      <c r="B130" s="17"/>
+      <c r="C130" s="11" t="s">
         <v>660</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="E130" s="12" t="s">
+      <c r="E130" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F130" s="41" t="s">
+      <c r="F130" s="25" t="s">
         <v>662</v>
       </c>
-      <c r="G130" s="31"/>
-      <c r="H130" s="19"/>
-      <c r="I130" s="15" t="s">
+      <c r="G130" s="13"/>
+      <c r="H130" s="11"/>
+      <c r="I130" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J130" s="16"/>
-      <c r="K130" s="12"/>
+      <c r="J130" s="14"/>
+      <c r="K130" s="11"/>
     </row>
     <row r="131" customHeight="1" spans="1:11">
-      <c r="A131" s="34"/>
-      <c r="B131" s="28"/>
-      <c r="C131" s="12" t="s">
+      <c r="A131" s="19"/>
+      <c r="B131" s="17"/>
+      <c r="C131" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="D131" s="12" t="s">
+      <c r="D131" s="11" t="s">
         <v>664</v>
       </c>
-      <c r="E131" s="12" t="s">
+      <c r="E131" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="F131" s="13" t="s">
+      <c r="F131" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="G131" s="14" t="s">
+      <c r="G131" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="H131" s="12" t="s">
+      <c r="H131" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I131" s="17"/>
-      <c r="J131" s="18"/>
-      <c r="K131" s="17"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="14"/>
+      <c r="K131" s="11"/>
     </row>
     <row r="132" customHeight="1" spans="1:11">
-      <c r="A132" s="32"/>
-      <c r="B132" s="28"/>
-      <c r="C132" s="12" t="s">
+      <c r="A132" s="19"/>
+      <c r="B132" s="17"/>
+      <c r="C132" s="11" t="s">
         <v>668</v>
       </c>
-      <c r="D132" s="19"/>
-      <c r="E132" s="12" t="s">
+      <c r="D132" s="11"/>
+      <c r="E132" s="11" t="s">
         <v>669</v>
       </c>
-      <c r="F132" s="13" t="s">
+      <c r="F132" s="12" t="s">
         <v>670</v>
       </c>
-      <c r="G132" s="29"/>
-      <c r="H132" s="19"/>
-      <c r="I132" s="16" t="s">
+      <c r="G132" s="13"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J132" s="16"/>
-      <c r="K132" s="12" t="s">
+      <c r="J132" s="14"/>
+      <c r="K132" s="11" t="s">
         <v>671</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:11">
-      <c r="A133" s="34"/>
-      <c r="B133" s="28"/>
-      <c r="C133" s="12" t="s">
+      <c r="A133" s="19"/>
+      <c r="B133" s="17"/>
+      <c r="C133" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D133" s="12" t="s">
+      <c r="D133" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E133" s="12" t="s">
+      <c r="E133" s="11" t="s">
         <v>665</v>
       </c>
-      <c r="F133" s="13" t="s">
+      <c r="F133" s="12" t="s">
         <v>672</v>
       </c>
-      <c r="G133" s="29"/>
-      <c r="H133" s="12" t="s">
+      <c r="G133" s="13"/>
+      <c r="H133" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I133" s="19"/>
-      <c r="J133" s="18"/>
-      <c r="K133" s="19"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="14"/>
+      <c r="K133" s="11"/>
     </row>
     <row r="134" customHeight="1" spans="1:11">
-      <c r="A134" s="32"/>
-      <c r="B134" s="28"/>
-      <c r="C134" s="12" t="s">
+      <c r="A134" s="19"/>
+      <c r="B134" s="17"/>
+      <c r="C134" s="11" t="s">
         <v>673</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="11" t="s">
         <v>674</v>
       </c>
-      <c r="E134" s="12"/>
-      <c r="F134" s="41" t="s">
+      <c r="E134" s="11"/>
+      <c r="F134" s="25" t="s">
         <v>675</v>
       </c>
-      <c r="G134" s="25" t="s">
+      <c r="G134" s="13" t="s">
         <v>676</v>
       </c>
-      <c r="H134" s="12" t="s">
+      <c r="H134" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="I134" s="15"/>
-      <c r="J134" s="16"/>
-      <c r="K134" s="12" t="s">
+      <c r="I134" s="14"/>
+      <c r="J134" s="14"/>
+      <c r="K134" s="11" t="s">
         <v>677</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:11">
-      <c r="A135" s="32"/>
-      <c r="B135" s="28"/>
-      <c r="C135" s="12" t="s">
+      <c r="A135" s="19"/>
+      <c r="B135" s="17"/>
+      <c r="C135" s="11" t="s">
         <v>678</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="11" t="s">
         <v>679</v>
       </c>
-      <c r="E135" s="12"/>
-      <c r="F135" s="41" t="s">
+      <c r="E135" s="11"/>
+      <c r="F135" s="25" t="s">
         <v>675</v>
       </c>
-      <c r="G135" s="31"/>
-      <c r="H135" s="12" t="s">
+      <c r="G135" s="13"/>
+      <c r="H135" s="11" t="s">
         <v>680</v>
       </c>
-      <c r="I135" s="15"/>
-      <c r="J135" s="16"/>
-      <c r="K135" s="20"/>
+      <c r="I135" s="14"/>
+      <c r="J135" s="14"/>
+      <c r="K135" s="15"/>
     </row>
     <row r="136" customHeight="1" spans="1:11">
-      <c r="A136" s="32"/>
-      <c r="B136" s="28"/>
-      <c r="C136" s="12" t="s">
+      <c r="A136" s="19"/>
+      <c r="B136" s="17"/>
+      <c r="C136" s="11" t="s">
         <v>681</v>
       </c>
-      <c r="D136" s="12" t="s">
+      <c r="D136" s="11" t="s">
         <v>682</v>
       </c>
-      <c r="E136" s="12" t="s">
+      <c r="E136" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F136" s="41" t="s">
+      <c r="F136" s="25" t="s">
         <v>683</v>
       </c>
-      <c r="G136" s="14" t="s">
+      <c r="G136" s="13" t="s">
         <v>684</v>
       </c>
-      <c r="H136" s="12" t="s">
+      <c r="H136" s="11" t="s">
         <v>685</v>
       </c>
-      <c r="I136" s="15"/>
-      <c r="J136" s="16" t="s">
+      <c r="I136" s="14"/>
+      <c r="J136" s="14" t="s">
         <v>686</v>
       </c>
-      <c r="K136" s="12" t="s">
+      <c r="K136" s="11" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:11">
-      <c r="A137" s="32"/>
-      <c r="B137" s="28"/>
-      <c r="C137" s="12" t="s">
+      <c r="A137" s="19"/>
+      <c r="B137" s="17"/>
+      <c r="C137" s="11" t="s">
         <v>688</v>
       </c>
-      <c r="D137" s="12" t="s">
+      <c r="D137" s="11" t="s">
         <v>689</v>
       </c>
-      <c r="E137" s="12"/>
-      <c r="F137" s="41" t="s">
+      <c r="E137" s="11"/>
+      <c r="F137" s="25" t="s">
         <v>690</v>
       </c>
-      <c r="G137" s="29"/>
-      <c r="H137" s="12" t="s">
+      <c r="G137" s="13"/>
+      <c r="H137" s="11" t="s">
         <v>691</v>
       </c>
-      <c r="I137" s="15" t="s">
+      <c r="I137" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J137" s="16"/>
-      <c r="K137" s="16" t="s">
+      <c r="J137" s="14"/>
+      <c r="K137" s="14" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:11">
-      <c r="A138" s="32"/>
-      <c r="B138" s="28"/>
-      <c r="C138" s="16" t="s">
+      <c r="A138" s="19"/>
+      <c r="B138" s="17"/>
+      <c r="C138" s="14" t="s">
         <v>693</v>
       </c>
-      <c r="D138" s="12" t="s">
+      <c r="D138" s="11" t="s">
         <v>694</v>
       </c>
-      <c r="E138" s="12"/>
-      <c r="F138" s="13" t="s">
+      <c r="E138" s="11"/>
+      <c r="F138" s="12" t="s">
         <v>695</v>
       </c>
-      <c r="G138" s="32"/>
-      <c r="H138" s="12" t="s">
+      <c r="G138" s="19"/>
+      <c r="H138" s="11" t="s">
         <v>696</v>
       </c>
-      <c r="I138" s="15" t="s">
+      <c r="I138" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J138" s="16"/>
-      <c r="K138" s="12" t="s">
+      <c r="J138" s="14"/>
+      <c r="K138" s="11" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:11">
-      <c r="A139" s="32"/>
-      <c r="B139" s="28"/>
-      <c r="C139" s="16" t="s">
+      <c r="A139" s="19"/>
+      <c r="B139" s="17"/>
+      <c r="C139" s="14" t="s">
         <v>698</v>
       </c>
-      <c r="D139" s="12" t="s">
+      <c r="D139" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="E139" s="12" t="s">
+      <c r="E139" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F139" s="41" t="s">
+      <c r="F139" s="25" t="s">
         <v>700</v>
       </c>
-      <c r="G139" s="29"/>
-      <c r="H139" s="19"/>
-      <c r="I139" s="15" t="s">
+      <c r="G139" s="13"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J139" s="16"/>
-      <c r="K139" s="12" t="s">
+      <c r="J139" s="14"/>
+      <c r="K139" s="11" t="s">
         <v>701</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:11">
-      <c r="A140" s="32"/>
-      <c r="B140" s="28"/>
-      <c r="C140" s="12" t="s">
+      <c r="A140" s="19"/>
+      <c r="B140" s="17"/>
+      <c r="C140" s="11" t="s">
         <v>702</v>
       </c>
-      <c r="D140" s="12" t="s">
+      <c r="D140" s="11" t="s">
         <v>703</v>
       </c>
-      <c r="E140" s="12"/>
-      <c r="F140" s="41" t="s">
+      <c r="E140" s="11"/>
+      <c r="F140" s="25" t="s">
         <v>704</v>
       </c>
-      <c r="G140" s="14" t="s">
+      <c r="G140" s="18" t="s">
         <v>705</v>
       </c>
-      <c r="H140" s="12" t="s">
+      <c r="H140" s="11" t="s">
         <v>706</v>
       </c>
-      <c r="I140" s="15"/>
-      <c r="J140" s="16" t="s">
+      <c r="I140" s="14"/>
+      <c r="J140" s="14" t="s">
         <v>707</v>
       </c>
-      <c r="K140" s="12" t="s">
+      <c r="K140" s="11" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:11">
-      <c r="A141" s="32"/>
-      <c r="B141" s="28"/>
-      <c r="C141" s="16" t="s">
+      <c r="A141" s="19"/>
+      <c r="B141" s="17"/>
+      <c r="C141" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="D141" s="12" t="s">
+      <c r="D141" s="11" t="s">
         <v>710</v>
       </c>
-      <c r="E141" s="12"/>
-      <c r="F141" s="41" t="s">
+      <c r="E141" s="11"/>
+      <c r="F141" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="G141" s="31"/>
-      <c r="H141" s="12" t="s">
+      <c r="G141" s="13"/>
+      <c r="H141" s="11" t="s">
         <v>711</v>
       </c>
-      <c r="I141" s="15"/>
-      <c r="J141" s="16"/>
-      <c r="K141" s="35" t="s">
+      <c r="I141" s="14"/>
+      <c r="J141" s="14"/>
+      <c r="K141" s="20" t="s">
         <v>712</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:11">
-      <c r="A142" s="32"/>
-      <c r="B142" s="28"/>
-      <c r="C142" s="12" t="s">
+      <c r="A142" s="19"/>
+      <c r="B142" s="17"/>
+      <c r="C142" s="11" t="s">
         <v>713</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="D142" s="11" t="s">
         <v>714</v>
       </c>
-      <c r="E142" s="12" t="s">
+      <c r="E142" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F142" s="41" t="s">
+      <c r="F142" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="G142" s="29"/>
-      <c r="H142" s="12" t="s">
+      <c r="G142" s="13"/>
+      <c r="H142" s="11" t="s">
         <v>715</v>
       </c>
-      <c r="I142" s="15"/>
-      <c r="J142" s="16"/>
-      <c r="K142" s="12" t="s">
+      <c r="I142" s="14"/>
+      <c r="J142" s="14"/>
+      <c r="K142" s="11" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="1:11">
-      <c r="A143" s="32"/>
-      <c r="B143" s="28"/>
-      <c r="C143" s="16" t="s">
+      <c r="A143" s="19"/>
+      <c r="B143" s="17"/>
+      <c r="C143" s="14" t="s">
         <v>717</v>
       </c>
-      <c r="D143" s="12" t="s">
+      <c r="D143" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E143" s="12" t="s">
+      <c r="E143" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F143" s="41" t="s">
+      <c r="F143" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="G143" s="14" t="s">
+      <c r="G143" s="13" t="s">
         <v>718</v>
       </c>
-      <c r="H143" s="12" t="s">
+      <c r="H143" s="11" t="s">
         <v>719</v>
       </c>
-      <c r="I143" s="15" t="s">
+      <c r="I143" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J143" s="16"/>
-      <c r="K143" s="12" t="s">
+      <c r="J143" s="14"/>
+      <c r="K143" s="11" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:11">
-      <c r="A144" s="32"/>
-      <c r="B144" s="28"/>
-      <c r="C144" s="12" t="s">
+      <c r="A144" s="19"/>
+      <c r="B144" s="17"/>
+      <c r="C144" s="11" t="s">
         <v>721</v>
       </c>
-      <c r="D144" s="12" t="s">
+      <c r="D144" s="11" t="s">
         <v>722</v>
       </c>
-      <c r="E144" s="12"/>
-      <c r="F144" s="13" t="s">
+      <c r="E144" s="11"/>
+      <c r="F144" s="12" t="s">
         <v>723</v>
       </c>
-      <c r="G144" s="25" t="s">
+      <c r="G144" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="H144" s="16" t="s">
+      <c r="H144" s="14" t="s">
         <v>725</v>
       </c>
-      <c r="I144" s="15"/>
-      <c r="J144" s="16"/>
-      <c r="K144" s="12"/>
+      <c r="I144" s="14"/>
+      <c r="J144" s="14"/>
+      <c r="K144" s="11"/>
     </row>
     <row r="145" customHeight="1" spans="1:11">
-      <c r="A145" s="32"/>
-      <c r="B145" s="28"/>
-      <c r="C145" s="12" t="s">
+      <c r="A145" s="19"/>
+      <c r="B145" s="17"/>
+      <c r="C145" s="11" t="s">
         <v>726</v>
       </c>
-      <c r="D145" s="12"/>
-      <c r="E145" s="12" t="s">
+      <c r="D145" s="11"/>
+      <c r="E145" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F145" s="41" t="s">
+      <c r="F145" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="G145" s="29"/>
-      <c r="H145" s="19"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="16"/>
-      <c r="K145" s="16" t="s">
+      <c r="G145" s="13"/>
+      <c r="H145" s="11"/>
+      <c r="I145" s="14"/>
+      <c r="J145" s="14"/>
+      <c r="K145" s="14" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:11">
-      <c r="A146" s="32"/>
-      <c r="B146" s="28"/>
-      <c r="C146" s="16" t="s">
+      <c r="A146" s="19"/>
+      <c r="B146" s="17"/>
+      <c r="C146" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="D146" s="12" t="s">
+      <c r="D146" s="11" t="s">
         <v>730</v>
       </c>
-      <c r="E146" s="12" t="s">
+      <c r="E146" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F146" s="41" t="s">
+      <c r="F146" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="G146" s="26" t="s">
+      <c r="G146" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="H146" s="12" t="s">
+      <c r="H146" s="11" t="s">
         <v>731</v>
       </c>
-      <c r="I146" s="15"/>
-      <c r="J146" s="16"/>
-      <c r="K146" s="12" t="s">
+      <c r="I146" s="14"/>
+      <c r="J146" s="14"/>
+      <c r="K146" s="11" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:11">
-      <c r="A147" s="32"/>
-      <c r="B147" s="28"/>
-      <c r="C147" s="12" t="s">
+      <c r="A147" s="19"/>
+      <c r="B147" s="17"/>
+      <c r="C147" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="D147" s="12" t="s">
+      <c r="D147" s="11" t="s">
         <v>734</v>
       </c>
-      <c r="E147" s="12" t="s">
+      <c r="E147" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="F147" s="13" t="s">
+      <c r="F147" s="12" t="s">
         <v>736</v>
       </c>
-      <c r="G147" s="14" t="s">
+      <c r="G147" s="13" t="s">
         <v>737</v>
       </c>
-      <c r="H147" s="12" t="s">
+      <c r="H147" s="11" t="s">
         <v>738</v>
       </c>
-      <c r="I147" s="15"/>
-      <c r="J147" s="16" t="s">
+      <c r="I147" s="14"/>
+      <c r="J147" s="14" t="s">
         <v>739</v>
       </c>
-      <c r="K147" s="16" t="s">
+      <c r="K147" s="14" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:11">
-      <c r="A148" s="32"/>
-      <c r="B148" s="28"/>
-      <c r="C148" s="16" t="s">
+      <c r="A148" s="19"/>
+      <c r="B148" s="17"/>
+      <c r="C148" s="14" t="s">
         <v>741</v>
       </c>
-      <c r="D148" s="12" t="s">
+      <c r="D148" s="11" t="s">
         <v>742</v>
       </c>
-      <c r="E148" s="12" t="s">
+      <c r="E148" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F148" s="13" t="s">
+      <c r="F148" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="G148" s="29"/>
-      <c r="H148" s="19"/>
-      <c r="I148" s="15" t="s">
+      <c r="G148" s="13"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="J148" s="16"/>
-      <c r="K148" s="12" t="s">
+      <c r="J148" s="14"/>
+      <c r="K148" s="11" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:11">
-      <c r="A149" s="32"/>
-      <c r="B149" s="28"/>
-      <c r="C149" s="12" t="s">
+      <c r="A149" s="19"/>
+      <c r="B149" s="17"/>
+      <c r="C149" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="D149" s="12" t="s">
+      <c r="D149" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="E149" s="12" t="s">
+      <c r="E149" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F149" s="13" t="s">
+      <c r="F149" s="12" t="s">
         <v>747</v>
       </c>
-      <c r="G149" s="14" t="s">
+      <c r="G149" s="13" t="s">
         <v>748</v>
       </c>
-      <c r="H149" s="19"/>
-      <c r="I149" s="15"/>
-      <c r="J149" s="16"/>
-      <c r="K149" s="12" t="s">
+      <c r="H149" s="11"/>
+      <c r="I149" s="14"/>
+      <c r="J149" s="14"/>
+      <c r="K149" s="11" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:11">
-      <c r="A150" s="32"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="12" t="s">
+      <c r="A150" s="19"/>
+      <c r="B150" s="17"/>
+      <c r="C150" s="11" t="s">
         <v>750</v>
       </c>
-      <c r="D150" s="12" t="s">
+      <c r="D150" s="11" t="s">
         <v>751</v>
       </c>
-      <c r="E150" s="12" t="s">
+      <c r="E150" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F150" s="41" t="s">
+      <c r="F150" s="25" t="s">
         <v>752</v>
       </c>
-      <c r="G150" s="14" t="s">
+      <c r="G150" s="13" t="s">
         <v>753</v>
       </c>
-      <c r="H150" s="16" t="s">
+      <c r="H150" s="14" t="s">
         <v>754</v>
       </c>
-      <c r="I150" s="15"/>
-      <c r="J150" s="16"/>
-      <c r="K150" s="16" t="s">
+      <c r="I150" s="14"/>
+      <c r="J150" s="14"/>
+      <c r="K150" s="14" t="s">
         <v>755</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:11">
-      <c r="A151" s="32"/>
-      <c r="B151" s="28"/>
-      <c r="C151" s="12" t="s">
+      <c r="A151" s="19"/>
+      <c r="B151" s="17"/>
+      <c r="C151" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="D151" s="11" t="s">
         <v>757</v>
       </c>
-      <c r="E151" s="12"/>
-      <c r="F151" s="13"/>
-      <c r="G151" s="34"/>
-      <c r="H151" s="26" t="s">
+      <c r="E151" s="11"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="19"/>
+      <c r="H151" s="13" t="s">
         <v>758</v>
       </c>
-      <c r="I151" s="15"/>
-      <c r="J151" s="16" t="s">
+      <c r="I151" s="14"/>
+      <c r="J151" s="14" t="s">
         <v>759</v>
       </c>
-      <c r="K151" s="12" t="s">
+      <c r="K151" s="11" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:11">
-      <c r="A152" s="34"/>
-      <c r="B152" s="36" t="s">
+      <c r="A152" s="19"/>
+      <c r="B152" s="21" t="s">
         <v>761</v>
       </c>
-      <c r="C152" s="37" t="s">
+      <c r="C152" s="22" t="s">
         <v>762</v>
       </c>
-      <c r="D152" s="38" t="s">
+      <c r="D152" s="15" t="s">
         <v>763</v>
       </c>
-      <c r="E152" s="20"/>
-      <c r="F152" s="39"/>
-      <c r="G152" s="34"/>
-      <c r="H152" s="20"/>
-      <c r="I152" s="20"/>
-      <c r="J152" s="40"/>
-      <c r="K152" s="20"/>
+      <c r="E152" s="15"/>
+      <c r="F152" s="23"/>
+      <c r="G152" s="19"/>
+      <c r="H152" s="15"/>
+      <c r="I152" s="15"/>
+      <c r="J152" s="24"/>
+      <c r="K152" s="15"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K152" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:K152">
+    <sortState ref="A1:K152">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -8562,8 +8478,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 J1:K1" numberStoredAsText="1"/>
-    <ignoredError sqref="H1:I1" numberStoredAsText="1" emptyCellReference="1"/>
+    <ignoredError sqref="A1:K42 A43:F43 H43:K43 A44:K54 A55:F55 H55:K55 A56:K56 A57:F57 H57:K57 A58:K65 A66:F66 H66:K66 A67:K69 A70:F70 H70:K70 A71:K71 A72:F72 H72:K72 A73:K73 A74:F75 H74:K75 A76:K76 A77:F77 H77:K77 A78:K102 A103:F103 H103:K103 A104:K104 A105:F105 H105:K105 A106:K122 A123:F124 H123:K123 H124:J124 A125:K139 A140:F140 H140:K140 A141:K152" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/xlsx/shosta.xlsx
+++ b/xlsx/shosta.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$173</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="885">
   <si>
     <t>sort</t>
   </si>
@@ -2995,13 +2995,483 @@
     <t>Opera in two acts compiled by Sofia Khentova (1980)</t>
   </si>
   <si>
+    <t>the Gamblers</t>
+  </si>
+  <si>
+    <t>Игроки</t>
+  </si>
+  <si>
+    <t>28 december 1941 – June 1942</t>
+  </si>
+  <si>
+    <t>act i
+1. Introduction Allegretto 
+2. Scenes in the hotel (figs. 8-104)
+3. Card gambling Scene</t>
+  </si>
+  <si>
+    <t>3(II=picc,III=afl).3(II=corA).4(III=Ebcl,IV=bcl).3(III=dbn)-4.3.3.1-timp.
+perc:tgl/cast/tamb/SD/BD/cyms/xyl-bbalalaika-2hp-pft-strings</t>
+  </si>
+  <si>
+    <t>Opera after Nikolai Gogol’s comedy
+Libretto by the composer</t>
+  </si>
+  <si>
+    <t>native leningrad, Op. 63</t>
+  </si>
+  <si>
+    <t>Родной Ленинград. Вокално-симфоническая сюита из театрализованной программы 
+«Отчизна», Соч. 63</t>
+  </si>
+  <si>
+    <t>october 1942</t>
+  </si>
+  <si>
+    <t>1. Overture Moderato non troppo · Più mosso
+2. Song of Victorious October Allegretto
+3. Dance of the Youth Moderato · Allegro con brio · Molto meno mosso
+4. Ode to Leningrad Moderato</t>
+  </si>
+  <si>
+    <t>1.picc.1.2.1-2.3.3.1-timp.perc:tgl/tamb/SD/BD/cyms-balalaikas(adlib.)-pft
+strings-tenor, bass, mixed choir</t>
+  </si>
+  <si>
+    <t>Written as a tribute to the courage of the citizens of Leningrad</t>
+  </si>
+  <si>
+    <t>Suite from the NKVD Song and Dance Ensemble Show ‘Motherland’</t>
+  </si>
+  <si>
+    <t>6 romances on verses by w. raleigh, 
+r. burns and w. shakespeare, Op. 62</t>
+  </si>
+  <si>
+    <t>Шесть романсов на слова У. Ралея, Р. Бёрнса и У. Шекспира для баса и 
+фортепиано, Соч. 62</t>
+  </si>
+  <si>
+    <t>7 may - 25 october 1942</t>
+  </si>
+  <si>
+    <t>1. The Wood, the Weed, the Wag (Sir Walter Raleigh to His Sonne) Largo (q = 54)
+2. O, Wert Thou in the Cauld Blast Moderato (q . = 76)
+3. McPherson before His Execution (McPherson’s Farewell) Allegretto (q = 112)
+4. Jenny (Comin’ thro’ the Rye) Moderato (q = 104)
+5. Sonnet LXVI (Tyr’d with all these) Lento (h = 66)
+6. The King’s Campaign (‘The Grand Old Duke of York’ or ‘The King of France went up the Hill’) Allegretto (q = 126)</t>
+  </si>
+  <si>
+    <t>for bass and piano</t>
+  </si>
+  <si>
+    <t>to Levon Tadevosovich Atovmyan (No. 1), 
+to Nina Vasilievna Shostakovich (No. 2),
+to Isaac Davidovich Glikman (No. 3), 
+to Yuri Vasilievich Sviridov (No. 4), 
+to Ivan Ivanovich Sollertinsky (No. 5),
+to Vissarion Yakovlevich Shebalin (No. 6)</t>
+  </si>
+  <si>
+    <t>62a</t>
+  </si>
+  <si>
+    <t>6 romances on verses by w. raleigh, 
+r. burns and w. shakespeare, Op. 62a</t>
+  </si>
+  <si>
+    <t>Шесть романсов на слова У. Ралея, Р. Бёрнса и У. Шекспира для баса и 
+симфонического оркестра, Соч. 62а</t>
+  </si>
+  <si>
+    <t>arkhangelskoe</t>
+  </si>
+  <si>
+    <t>18 march 1943</t>
+  </si>
+  <si>
+    <t>3(III=picc).3(III=corA).4(III=Ebcl,IV=bcl).3(III=dbn)-4.3.3.1-timp.perc:tgl/
+tamb/SD/BD/cyms/tam-t/xyl-2hp-cel-strings</t>
+  </si>
+  <si>
+    <t>sonata For piano no. 2 in B minor, Op. 61</t>
+  </si>
+  <si>
+    <t>Соната для фортепиано № 2, Соч. 61</t>
+  </si>
+  <si>
+    <t>kuibyshev/arkhangelskoe</t>
+  </si>
+  <si>
+    <t>January – 17 march 1943</t>
+  </si>
+  <si>
+    <t>1. Allegretto
+2. Largo
+3. Moderato (con moto) · Allegretto con moto · Adagio · Moderato</t>
+  </si>
+  <si>
+    <t>Dedicated to the memory of Leonid Vladimirovich Nikolaev</t>
+  </si>
+  <si>
+    <t>8 british and american Folksongs</t>
+  </si>
+  <si>
+    <t>Восемь английских и американских народних песен</t>
+  </si>
+  <si>
+    <t>12 may/July 1943</t>
+  </si>
+  <si>
+    <t>1. The Sailor’s Bride [Nevesta moryaka] Allegretto
+2. John Anderson Lento, espressivo
+3. Billy Boy Vivo
+4. Oh, the Oak and the Ash [O, moi yasen i dub] Moderato
+5. King Arthur’s Servants [Slugi Korolya Artura] Vivo
+6. Comin’ thro’ the Rye [Vidno, rozhyu shla] Moderato
+7. Spring Round Dance [Vesenni khorovod] Allegro
+8. When Johnny Comes Marching Home Again [K nam Dzhonni pridyot opyat] Allegretto</t>
+  </si>
+  <si>
+    <t>for soprano (Nos. 1-7), bass (No. 8) and chamber orchestra
+2.2(II=corA).2.2-4.1.0.0-timp.perc:tgl/tamb/glsp-hp-strings</t>
+  </si>
+  <si>
+    <t>Texts by 
+William Julius Mickle (No. 1), 
+Robert Burns (Nos. 2, 6), 
+Patrick Sarsfield Gilmore (No. 8), 
+Northumbrian capstan shanty (No. 3), 
+English Air (No. 4), 
+‘Three Sons of Rogues’ (No. 5) 
+‘Come Lasses and Lads’ (No. 7)
+Translations by 
+Samuil Bolotin (Nos. 1, 2, 4, 5, 8), 
+Tatyana Sikorskaya (Nos. 2, 3, 5, 7),
+Samuil Marshak (No. 6)</t>
+  </si>
+  <si>
+    <t>symphony no. 8 in C minor, Op. 65</t>
+  </si>
+  <si>
+    <t>Симфония № 8, Соч. 65</t>
+  </si>
+  <si>
+    <t>ivanovo-moscow</t>
+  </si>
+  <si>
+    <t>2 July  - 9 september 1943</t>
+  </si>
+  <si>
+    <t>1. Adagio (q = 80) · Poco più mosso (q = 72) · Adagio (q = 32) · Allegro non troppo (q = 116) · Allegro (h = 69) · Adagio (e = 80) · Poco più mosso (e = 72) · Adagio (e = 80 · q = 56)
+2. Allegretto (q = 132 · q = 144) · L’istesso tempo
+3. Allegro non troppo (h = 152) attacca
+4. Largo (q = 50) attacca
+5. Allegretto (q = 136 · q = 152 · q = 168) · L’istesso tempo · Allegro (h = 108) · Adagio (q = 60) · Più mosso (h = 60) · Adagio (q = 60) Allegretto (q = 96 · q = 168 · q = 152) · Andante (q = 84)</t>
+  </si>
+  <si>
+    <t>4(III,IV=picc).2.corA.2.Ebcl.bcl.2.dbn-4.3.3.1-timp.perc:tgl/tamb/SD/BD/
+cym/susp.cym/tam-t/xyl-strings(16.14.12.12.10)</t>
+  </si>
+  <si>
+    <t>Dedicated to Evgeni Alexandrovich Mravinsky</t>
+  </si>
+  <si>
+    <t>anthem oF the soviet union (i) ‘Glory to Our Soviet Motherland’ 
+in G major</t>
+  </si>
+  <si>
+    <t>Гимн Советского Союза «Славься, отчизна Советов»</t>
+  </si>
+  <si>
+    <t>1943</t>
+  </si>
+  <si>
+    <t>Moderato (q = 96)</t>
+  </si>
+  <si>
+    <t>for mixed choir and orchestra
+3(III=picc).3.3.2-4.3.3.1.timp.perc:tgl/SD/cyms-strings</t>
+  </si>
+  <si>
+    <t>Text by Evgeni Dolmatovsky</t>
+  </si>
+  <si>
+    <t>anthem oF the soviet union (ii) ‘Unbreakable Union of Freeborn 
+Republics’ in E flat major</t>
+  </si>
+  <si>
+    <t>Гимн Советского Союза «Союз нерушимый, республик свободных»</t>
+  </si>
+  <si>
+    <t>for mixed choir and orchestra
+3(III=picc).3(III=corA).4(III=Ebclar,IV=bcl).3(III=dbn)-4.3.3.1-timp.perc:tgl/
+SD/BD/cyms-strings</t>
+  </si>
+  <si>
+    <t>Text by Sergei Mikhalkov and El-Registan</t>
+  </si>
+  <si>
+    <t>invincible red army</t>
+  </si>
+  <si>
+    <t>Армия Красная, непобедимая</t>
+  </si>
+  <si>
+    <t>1943(?)</t>
+  </si>
+  <si>
+    <t>for voice (choir) and piano</t>
+  </si>
+  <si>
+    <t>jointly composed by Dmitri Shostakovich and Aram Khachaturyan
+Text by Mikhail Golodny</t>
+  </si>
+  <si>
+    <t>rothschild’s violin</t>
+  </si>
+  <si>
+    <t>В. И. Флейшман. Скрипка Ротшильда</t>
+  </si>
+  <si>
+    <t>kuibyshev - moscow</t>
+  </si>
+  <si>
+    <t>1942 - 5 February 1944 (?)</t>
+  </si>
+  <si>
+    <t>3(III=picc).3(III=corA).3(III=Ebcl).3(III=dbn)-4.3.3.1-timp.perc:tgl/tamb/SD/
+BD/cyms/glsp-hp-strings</t>
+  </si>
+  <si>
+    <t>[veniamin fleishman (1913-1941)] 
+Opera in one act, completed and partly orchestrated
+Libretto after Anton Chekhov by Alexander Preis</t>
+  </si>
+  <si>
+    <t>Zoya, Op. 64</t>
+  </si>
+  <si>
+    <t>Зоя. Музыка к кинофильму, Соч. 64</t>
+  </si>
+  <si>
+    <t>Moscow</t>
+  </si>
+  <si>
+    <t>June 1944</t>
+  </si>
+  <si>
+    <t>1. [No. 1] Allegretto
+2. [No. 2] Moderato
+3. [No. 3] Adagio
+4. [No. 4] Moderato
+5. [No. 5] Moderato
+6. [No. 6] Moderato · Allegro · Presto
+7. Victory Adagio [No. 7]
+8. Belfry Allegro [No. 8]
+9. [No. 12] Moderato
+10. [No. 13] Moderato
+11. [No. 16] Allegretto
+12. Dneprostroi Allegretto [No. 20]
+13. [No. 21] Adagio
+14. Parade of First of May Allegretto [No. 22]
+15. Arrival of the Heroes Allegro [No. 23]
+16. [No. 24] Allegro
+17. Remembrance Moderato · Allegro [No. 25]
+18. Moscow Adagio [No. 30]
+19. Zoya’s Song Moderato con moto [No. 31]
+20. [No. 35] [con moto]</t>
+  </si>
+  <si>
+    <t>3(III=picc).3.4(Ebcl).3(III=dbn)-4.5.5.2-timp.perc:tgl/SD/BD/cyms/tam-t/glsp/
+xyl-2hp-strings-mixed choir</t>
+  </si>
+  <si>
+    <t>64a</t>
+  </si>
+  <si>
+    <t>suite From ‘Zoya’, Op. 64a</t>
+  </si>
+  <si>
+    <t>Сюита из музыки к кинофильму «Зоя»</t>
+  </si>
+  <si>
+    <t>1. Prelude ‘Song about Zoya’ Adagio · Moderato con moto
+2. Scene ‘Military Problem’ Allegretto · Allegro
+3. Prelude ‘Tragedy of a Loss’ Adagio
+4. March ‘Hero’s Victory’ Tempo di Marcia
+5. Finale ‘The Heroine’s Immortality’ Adagio</t>
+  </si>
+  <si>
+    <t>2.picc.3.3(III=bcl).Ebcl.2.dbn-4.5.5.2-timp.perc:tgl/tamb/SD/cyms/BD/glsp/
+tam-t/xyl-2hp-strings</t>
+  </si>
+  <si>
+    <t>for orchestra with choir (in No. 1) – assembled by Levon Atovmyan (1944 [?])</t>
+  </si>
+  <si>
+    <t>piano trio no. 2 in E minor, Op. 67</t>
+  </si>
+  <si>
+    <t>Трио № 2 для скрипки, виолончели и фортепиано, Соч. 67</t>
+  </si>
+  <si>
+    <t>moscow/ivanovo</t>
+  </si>
+  <si>
+    <t>december 1943 - 13 august 1944</t>
+  </si>
+  <si>
+    <t>1. Andante (q = 69) · Moderato (q = 96) · Poco più mosso (q = 160)
+2. Allegro con brio (h . = 132)
+3. Largo (q = 112)
+4. Allegretto (e = 144 · e = 168) · Adagio (q = 69)</t>
+  </si>
+  <si>
+    <t>Dedicated to the memory of Ivan Ivanovich Sollertinsky</t>
+  </si>
+  <si>
+    <t>string quartet no. 2 in A major, Op. 68</t>
+  </si>
+  <si>
+    <t>Квартет № 2 для двух скрипок, альта и виолончели, Соч. 68</t>
+  </si>
+  <si>
+    <t>Ivanovo</t>
+  </si>
+  <si>
+    <t>september 1944</t>
+  </si>
+  <si>
+    <t>1. Overture Moderato con moto (q = 144)
+2. Recitative and Romance Adagio (q = 66-76) · q = 69 · Più mosso · Adagio
+3. Waltz Allegro (h . = 104)
+4. Theme with Variations Adagio (q = 72) · Moderato con moto (q = 116) · Allegretto · Più mosso (q = 160) · Più mosso (q = 168) · Allegro non troppo (h . = 76) · Allegro (h . = 126) · Adagio (q = 72)</t>
+  </si>
+  <si>
+    <t>Dedicated to Vissarion Yakovlevich Shebalin</t>
+  </si>
+  <si>
+    <t>russian river, Op. 66, Incidental music to the NKVD Song and Dance Ensemble Show ‘The Great Russian River’</t>
+  </si>
+  <si>
+    <t>Русская река. Музыка к театрализованной программе, Соч. 66</t>
+  </si>
+  <si>
+    <t>17 december 1944</t>
+  </si>
+  <si>
+    <t>1. March Allegretto
+2. Football Presto
+3. The Battle of Stalingrad Moderato · Allegro
+4. Waltz
+5. Final Song Moderato</t>
+  </si>
+  <si>
+    <t>1.picc.1.2.1-2.3.2.1-timp.perc:SD/BD/cyms-strings-choir</t>
+  </si>
+  <si>
+    <t>Scenario by Mikhail Volpin, Iosif Dobrovolsky (also lyrics of Nos. 3 and 5) and Ni
+kolai Erdman</t>
+  </si>
+  <si>
+    <t>song, "a toast to our motherland"</t>
+  </si>
+  <si>
+    <t>Заздравнаяа песня о родине</t>
+  </si>
+  <si>
+    <t>1944</t>
+  </si>
+  <si>
+    <t>Presto</t>
+  </si>
+  <si>
+    <t>for tenor, mixed choir and piano</t>
+  </si>
+  <si>
+    <t>Text by Iosif Utkin</t>
+  </si>
+  <si>
+    <t>song, "the black sea"</t>
+  </si>
+  <si>
+    <t>Чёрное море</t>
+  </si>
+  <si>
+    <t>Allegro moderato</t>
+  </si>
+  <si>
+    <t>for bass, male choir and piano</t>
+  </si>
+  <si>
+    <t>annie laurie</t>
+  </si>
+  <si>
+    <t>Энни Лори</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molto moderato (e = 80)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for voice and chamber orchestra
+2.0.2.0-4.0.0.0-strings
+</t>
+  </si>
+  <si>
+    <t>Music and words by Lady John Scott after William Douglas of Fingland
+Russian translation by Nazari Raisky</t>
+  </si>
+  <si>
+    <t>children’s notebook, Op. 69</t>
+  </si>
+  <si>
+    <t>Детская тетрадь для фортепиано, Соч. 69</t>
+  </si>
+  <si>
+    <t>moscow</t>
+  </si>
+  <si>
+    <t>6 december 1944 (Nos. 1-6), 30 may 1945 (No. 7)</t>
+  </si>
+  <si>
+    <t>1.  March Allegretto
+2. Waltz Mopderato non troppo
+3. The Bear Allegretto
+4. Funny Story Allegro
+5. Sad Story Moderato
+6. Clockwork Doll Allegro
+7. Birthday Tempo di valse</t>
+  </si>
+  <si>
+    <t>symphony no. 9 in E flat major, Op. 70</t>
+  </si>
+  <si>
+    <t>Симфония № 9, Соч. 70</t>
+  </si>
+  <si>
+    <t>26 July – 30 august 1945</t>
+  </si>
+  <si>
+    <t>1. Allegro (h = 132)
+2. Moderato (q = 208) · Adagio (q = 152)
+3. Presto (q . = 126) attacca
+4. Largo (e = 84) attacca
+5. Allegretto (q = 100) · q = 126 · Pocchissimo animato · (Pocchissimo animato) · q = 108 · Allegro (q = 208)</t>
+  </si>
+  <si>
+    <t>2.picc.2.2.2-4.2.3.1-timp.perc(2):tgl/tamb/SD/BD/cym-strings(16-20.14-18.12-16.12-16.10-14)</t>
+  </si>
+  <si>
     <t>next</t>
   </si>
   <si>
     <t>https://www.boosey.com/downloads/schostakowitsch_werkverzeichnis.pdf</t>
   </si>
   <si>
-    <t>p.158</t>
+    <t>p.174</t>
   </si>
   <si>
     <t>61 sonata for piano no. 2 in B minor . . . . . . . . . . . . . . . . . . . . . . . . . . . (1943) . . 161 62 six romances on words by w. raleigh, r. burns and w. shakespeare for bass and piano . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1942) . . 160 62 a six romances on words by w. raleigh, r. burns and w. shakespeare for bass and symphony orchestra . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1943) . . 161 63 native leningrad Incidental music . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1942) . . 159 64 Zoya Music for the film . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1944) . . 167 64 a suite from ‘Zoya’ for orchestra with choir . . . . . . . . . . . . . . . . . . . . (1944[?]) . . 168 65 symphony no. 8 in C minor . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1943) . . 163 66 russian river Incidental music . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1944) . . 171 67 piano trio no. 2 in E minor . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1943-1944) . . 169 68 string quartet no. 2 in A major . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1944) . . 170 69 children’s notebook for piano . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1944/1945) . . 173 70 symphony no. 9 in E flat major . . . . . . . . . . . . . . . . . . . . . . . . . . . . . (1945) . . 174</t>
@@ -3054,7 +3524,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="MiSans VF Regular"/>
       <charset val="0"/>
     </font>
@@ -3668,7 +4138,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3733,6 +4203,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3745,6 +4221,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4272,7 +4751,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K152"/>
+  <dimension ref="A1:K173"/>
   <sheetFormatPr defaultColWidth="18.1441441441441" defaultRowHeight="35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.02702702702703" style="2" customWidth="1"/>
@@ -4281,7 +4760,7 @@
     <col min="5" max="5" width="13.972972972973" style="4" customWidth="1"/>
     <col min="6" max="6" width="34.972972972973" style="5" customWidth="1"/>
     <col min="7" max="7" width="13.036036036036" style="2" customWidth="1"/>
-    <col min="8" max="8" width="58.4594594594595" style="4" customWidth="1"/>
+    <col min="8" max="8" width="27.2522522522523" style="4" customWidth="1"/>
     <col min="9" max="9" width="24.7837837837838" style="4" customWidth="1"/>
     <col min="10" max="10" width="24.7837837837838" style="6" customWidth="1"/>
     <col min="11" max="11" width="35.0540540540541" style="4" customWidth="1"/>
@@ -4463,7 +4942,7 @@
       <c r="E6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="27" t="s">
         <v>38</v>
       </c>
       <c r="G6" s="13" t="s">
@@ -4494,7 +4973,7 @@
       <c r="E7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="27" t="s">
         <v>43</v>
       </c>
       <c r="G7" s="13" t="s">
@@ -4827,7 +5306,7 @@
       <c r="E18" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="27" t="s">
         <v>109</v>
       </c>
       <c r="G18" s="13" t="s">
@@ -4856,7 +5335,7 @@
       <c r="E19" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="27" t="s">
         <v>114</v>
       </c>
       <c r="G19" s="13" t="s">
@@ -5332,7 +5811,7 @@
       <c r="E35" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="27" t="s">
         <v>209</v>
       </c>
       <c r="G35" s="13" t="s">
@@ -5390,7 +5869,7 @@
         <v>220</v>
       </c>
       <c r="E37" s="11"/>
-      <c r="F37" s="25" t="s">
+      <c r="F37" s="27" t="s">
         <v>221</v>
       </c>
       <c r="G37" s="18" t="s">
@@ -5452,7 +5931,7 @@
       <c r="E39" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F39" s="27" t="s">
         <v>234</v>
       </c>
       <c r="G39" s="13" t="s">
@@ -5570,7 +6049,7 @@
       <c r="E43" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="F43" s="25" t="s">
+      <c r="F43" s="27" t="s">
         <v>259</v>
       </c>
       <c r="G43" s="18" t="s">
@@ -5949,7 +6428,7 @@
       <c r="E56" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F56" s="25" t="s">
+      <c r="F56" s="27" t="s">
         <v>326</v>
       </c>
       <c r="G56" s="13" t="s">
@@ -6096,7 +6575,7 @@
         <v>353</v>
       </c>
       <c r="E61" s="11"/>
-      <c r="F61" s="25" t="s">
+      <c r="F61" s="27" t="s">
         <v>354</v>
       </c>
       <c r="G61" s="13" t="s">
@@ -6216,7 +6695,7 @@
       <c r="E65" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F65" s="25" t="s">
+      <c r="F65" s="27" t="s">
         <v>375</v>
       </c>
       <c r="G65" s="13"/>
@@ -6270,7 +6749,7 @@
       <c r="E67" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F67" s="25" t="s">
+      <c r="F67" s="27" t="s">
         <v>385</v>
       </c>
       <c r="G67" s="13"/>
@@ -6297,7 +6776,7 @@
       <c r="E68" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F68" s="25" t="s">
+      <c r="F68" s="27" t="s">
         <v>375</v>
       </c>
       <c r="G68" s="13"/>
@@ -6324,7 +6803,7 @@
       <c r="E69" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F69" s="25" t="s">
+      <c r="F69" s="27" t="s">
         <v>391</v>
       </c>
       <c r="G69" s="13" t="s">
@@ -6500,7 +6979,7 @@
       <c r="E75" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F75" s="25" t="s">
+      <c r="F75" s="27" t="s">
         <v>424</v>
       </c>
       <c r="G75" s="18" t="s">
@@ -6587,7 +7066,7 @@
         <v>441</v>
       </c>
       <c r="E78" s="11"/>
-      <c r="F78" s="25" t="s">
+      <c r="F78" s="27" t="s">
         <v>442</v>
       </c>
       <c r="G78" s="13"/>
@@ -6714,7 +7193,7 @@
       <c r="E83" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F83" s="25" t="s">
+      <c r="F83" s="27" t="s">
         <v>462</v>
       </c>
       <c r="G83" s="13"/>
@@ -6737,7 +7216,7 @@
       <c r="E84" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F84" s="25" t="s">
+      <c r="F84" s="27" t="s">
         <v>465</v>
       </c>
       <c r="G84" s="13"/>
@@ -6760,7 +7239,7 @@
       <c r="E85" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="25" t="s">
+      <c r="F85" s="27" t="s">
         <v>468</v>
       </c>
       <c r="G85" s="13" t="s">
@@ -6787,7 +7266,7 @@
       <c r="E86" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F86" s="25" t="s">
+      <c r="F86" s="27" t="s">
         <v>468</v>
       </c>
       <c r="G86" s="13"/>
@@ -6812,7 +7291,7 @@
       <c r="E87" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F87" s="25" t="s">
+      <c r="F87" s="27" t="s">
         <v>468</v>
       </c>
       <c r="G87" s="13"/>
@@ -6837,7 +7316,7 @@
       <c r="E88" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F88" s="25" t="s">
+      <c r="F88" s="27" t="s">
         <v>468</v>
       </c>
       <c r="G88" s="13" t="s">
@@ -7332,7 +7811,7 @@
       <c r="E107" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F107" s="25" t="s">
+      <c r="F107" s="27" t="s">
         <v>552</v>
       </c>
       <c r="G107" s="13" t="s">
@@ -7430,7 +7909,7 @@
       <c r="E111" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F111" s="25" t="s">
+      <c r="F111" s="27" t="s">
         <v>565</v>
       </c>
       <c r="G111" s="13" t="s">
@@ -7484,7 +7963,7 @@
       <c r="E113" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F113" s="25" t="s">
+      <c r="F113" s="27" t="s">
         <v>576</v>
       </c>
       <c r="G113" s="13"/>
@@ -7605,7 +8084,7 @@
       <c r="E118" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F118" s="25" t="s">
+      <c r="F118" s="27" t="s">
         <v>601</v>
       </c>
       <c r="G118" s="13" t="s">
@@ -7632,7 +8111,7 @@
       <c r="E119" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F119" s="25" t="s">
+      <c r="F119" s="27" t="s">
         <v>259</v>
       </c>
       <c r="G119" s="13"/>
@@ -7761,7 +8240,7 @@
         <v>631</v>
       </c>
       <c r="E124" s="11"/>
-      <c r="F124" s="25" t="s">
+      <c r="F124" s="27" t="s">
         <v>632</v>
       </c>
       <c r="H124" s="11"/>
@@ -7785,7 +8264,7 @@
       <c r="E125" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F125" s="25" t="s">
+      <c r="F125" s="27" t="s">
         <v>637</v>
       </c>
       <c r="G125" s="13" t="s">
@@ -7812,7 +8291,7 @@
       <c r="E126" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F126" s="27" t="s">
         <v>644</v>
       </c>
       <c r="G126" s="13"/>
@@ -7910,7 +8389,7 @@
       <c r="E130" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F130" s="25" t="s">
+      <c r="F130" s="27" t="s">
         <v>662</v>
       </c>
       <c r="G130" s="13"/>
@@ -8002,7 +8481,7 @@
         <v>674</v>
       </c>
       <c r="E134" s="11"/>
-      <c r="F134" s="25" t="s">
+      <c r="F134" s="27" t="s">
         <v>675</v>
       </c>
       <c r="G134" s="13" t="s">
@@ -8027,7 +8506,7 @@
         <v>679</v>
       </c>
       <c r="E135" s="11"/>
-      <c r="F135" s="25" t="s">
+      <c r="F135" s="27" t="s">
         <v>675</v>
       </c>
       <c r="G135" s="13"/>
@@ -8050,7 +8529,7 @@
       <c r="E136" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F136" s="25" t="s">
+      <c r="F136" s="27" t="s">
         <v>683</v>
       </c>
       <c r="G136" s="13" t="s">
@@ -8077,7 +8556,7 @@
         <v>689</v>
       </c>
       <c r="E137" s="11"/>
-      <c r="F137" s="25" t="s">
+      <c r="F137" s="27" t="s">
         <v>690</v>
       </c>
       <c r="G137" s="13"/>
@@ -8129,7 +8608,7 @@
       <c r="E139" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F139" s="25" t="s">
+      <c r="F139" s="27" t="s">
         <v>700</v>
       </c>
       <c r="G139" s="13"/>
@@ -8152,7 +8631,7 @@
         <v>703</v>
       </c>
       <c r="E140" s="11"/>
-      <c r="F140" s="25" t="s">
+      <c r="F140" s="27" t="s">
         <v>704</v>
       </c>
       <c r="G140" s="18" t="s">
@@ -8179,7 +8658,7 @@
         <v>710</v>
       </c>
       <c r="E141" s="11"/>
-      <c r="F141" s="25" t="s">
+      <c r="F141" s="27" t="s">
         <v>424</v>
       </c>
       <c r="G141" s="13"/>
@@ -8204,7 +8683,7 @@
       <c r="E142" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F142" s="25" t="s">
+      <c r="F142" s="27" t="s">
         <v>424</v>
       </c>
       <c r="G142" s="13"/>
@@ -8229,7 +8708,7 @@
       <c r="E143" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F143" s="25" t="s">
+      <c r="F143" s="27" t="s">
         <v>424</v>
       </c>
       <c r="G143" s="13" t="s">
@@ -8279,7 +8758,7 @@
       <c r="E145" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F145" s="25" t="s">
+      <c r="F145" s="27" t="s">
         <v>727</v>
       </c>
       <c r="G145" s="13"/>
@@ -8302,7 +8781,7 @@
       <c r="E146" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F146" s="25" t="s">
+      <c r="F146" s="27" t="s">
         <v>727</v>
       </c>
       <c r="G146" s="13" t="s">
@@ -8408,7 +8887,7 @@
       <c r="E150" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F150" s="25" t="s">
+      <c r="F150" s="27" t="s">
         <v>752</v>
       </c>
       <c r="G150" s="13" t="s">
@@ -8448,37 +8927,619 @@
     </row>
     <row r="152" customHeight="1" spans="1:11">
       <c r="A152" s="19"/>
-      <c r="B152" s="21" t="s">
+      <c r="B152" s="17"/>
+      <c r="C152" s="11" t="s">
         <v>761</v>
       </c>
-      <c r="C152" s="22" t="s">
+      <c r="D152" s="11" t="s">
         <v>762</v>
       </c>
-      <c r="D152" s="15" t="s">
+      <c r="E152" t="s">
+        <v>735</v>
+      </c>
+      <c r="F152" s="12" t="s">
         <v>763</v>
       </c>
-      <c r="E152" s="15"/>
-      <c r="F152" s="23"/>
-      <c r="G152" s="19"/>
-      <c r="H152" s="15"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="24"/>
-      <c r="K152" s="15"/>
+      <c r="G152" s="13" t="s">
+        <v>764</v>
+      </c>
+      <c r="H152" s="18" t="s">
+        <v>765</v>
+      </c>
+      <c r="I152" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="J152" s="14"/>
+      <c r="K152" s="14" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="1:11">
+      <c r="A153" s="19">
+        <v>63</v>
+      </c>
+      <c r="B153" s="17">
+        <v>63</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="D153" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="E153" t="s">
+        <v>735</v>
+      </c>
+      <c r="F153" s="27" t="s">
+        <v>769</v>
+      </c>
+      <c r="G153" s="21" t="s">
+        <v>770</v>
+      </c>
+      <c r="H153" s="18" t="s">
+        <v>771</v>
+      </c>
+      <c r="I153" s="14"/>
+      <c r="J153" s="14" t="s">
+        <v>772</v>
+      </c>
+      <c r="K153" s="11" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:11">
+      <c r="A154" s="19">
+        <v>62</v>
+      </c>
+      <c r="B154" s="17">
+        <v>62</v>
+      </c>
+      <c r="C154" s="14" t="s">
+        <v>774</v>
+      </c>
+      <c r="D154" s="14" t="s">
+        <v>775</v>
+      </c>
+      <c r="E154" t="s">
+        <v>735</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="G154" s="21" t="s">
+        <v>777</v>
+      </c>
+      <c r="H154" s="13" t="s">
+        <v>778</v>
+      </c>
+      <c r="I154" s="14"/>
+      <c r="J154" s="14" t="s">
+        <v>779</v>
+      </c>
+      <c r="K154" s="11"/>
+    </row>
+    <row r="155" customHeight="1" spans="1:11">
+      <c r="A155" s="19">
+        <v>62.1</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="C155" s="14" t="s">
+        <v>781</v>
+      </c>
+      <c r="D155" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="E155" t="s">
+        <v>783</v>
+      </c>
+      <c r="F155" s="27" t="s">
+        <v>784</v>
+      </c>
+      <c r="G155" s="19"/>
+      <c r="H155" s="18" t="s">
+        <v>785</v>
+      </c>
+      <c r="I155" s="14"/>
+      <c r="J155" s="14"/>
+      <c r="K155" s="11"/>
+    </row>
+    <row r="156" customHeight="1" spans="1:11">
+      <c r="A156" s="19">
+        <v>61</v>
+      </c>
+      <c r="B156" s="17">
+        <v>61</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="D156" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="E156" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="F156" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="G156" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="H156" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I156" s="14"/>
+      <c r="J156" s="14" t="s">
+        <v>791</v>
+      </c>
+      <c r="K156" s="11"/>
+    </row>
+    <row r="157" customHeight="1" spans="1:11">
+      <c r="A157" s="19"/>
+      <c r="B157" s="17"/>
+      <c r="C157" s="11" t="s">
+        <v>792</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>793</v>
+      </c>
+      <c r="E157" s="11"/>
+      <c r="F157" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="G157" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="H157" s="18" t="s">
+        <v>796</v>
+      </c>
+      <c r="I157" s="14"/>
+      <c r="J157" s="14"/>
+      <c r="K157" s="14" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:11">
+      <c r="A158" s="19">
+        <v>65</v>
+      </c>
+      <c r="B158" s="17">
+        <v>65</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>798</v>
+      </c>
+      <c r="D158" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="E158" s="11" t="s">
+        <v>800</v>
+      </c>
+      <c r="F158" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="G158" s="21" t="s">
+        <v>802</v>
+      </c>
+      <c r="H158" s="18" t="s">
+        <v>803</v>
+      </c>
+      <c r="I158" s="14"/>
+      <c r="J158" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="K158" s="11"/>
+    </row>
+    <row r="159" customHeight="1" spans="1:11">
+      <c r="A159" s="19"/>
+      <c r="B159" s="17"/>
+      <c r="C159" s="14" t="s">
+        <v>805</v>
+      </c>
+      <c r="D159" s="11" t="s">
+        <v>806</v>
+      </c>
+      <c r="E159" s="11"/>
+      <c r="F159" s="27" t="s">
+        <v>807</v>
+      </c>
+      <c r="G159" s="21" t="s">
+        <v>808</v>
+      </c>
+      <c r="H159" s="18" t="s">
+        <v>809</v>
+      </c>
+      <c r="I159" s="14"/>
+      <c r="J159" s="14"/>
+      <c r="K159" s="14" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="1:11">
+      <c r="A160" s="19"/>
+      <c r="B160" s="17"/>
+      <c r="C160" s="14" t="s">
+        <v>811</v>
+      </c>
+      <c r="D160" s="11" t="s">
+        <v>812</v>
+      </c>
+      <c r="E160" s="11"/>
+      <c r="F160" s="27" t="s">
+        <v>807</v>
+      </c>
+      <c r="G160" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="H160" s="18" t="s">
+        <v>813</v>
+      </c>
+      <c r="I160" s="14"/>
+      <c r="J160" s="14"/>
+      <c r="K160" s="14" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="1:11">
+      <c r="A161" s="19"/>
+      <c r="B161" s="17"/>
+      <c r="C161" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="D161" s="11" t="s">
+        <v>816</v>
+      </c>
+      <c r="E161" s="11"/>
+      <c r="F161" s="27" t="s">
+        <v>817</v>
+      </c>
+      <c r="G161" s="19"/>
+      <c r="H161" s="18" t="s">
+        <v>818</v>
+      </c>
+      <c r="I161" s="14"/>
+      <c r="J161" s="14"/>
+      <c r="K161" s="14" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="1:11">
+      <c r="A162" s="19"/>
+      <c r="B162" s="17"/>
+      <c r="C162" s="14" t="s">
+        <v>820</v>
+      </c>
+      <c r="D162" s="11" t="s">
+        <v>821</v>
+      </c>
+      <c r="E162" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="G162" s="19"/>
+      <c r="H162" s="18" t="s">
+        <v>824</v>
+      </c>
+      <c r="I162" s="14"/>
+      <c r="J162" s="14"/>
+      <c r="K162" s="14" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="1:11">
+      <c r="A163" s="19">
+        <v>64</v>
+      </c>
+      <c r="B163" s="17">
+        <v>64</v>
+      </c>
+      <c r="C163" s="14" t="s">
+        <v>826</v>
+      </c>
+      <c r="D163" s="11" t="s">
+        <v>827</v>
+      </c>
+      <c r="E163" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="F163" s="28" t="s">
+        <v>829</v>
+      </c>
+      <c r="G163" s="18" t="s">
+        <v>830</v>
+      </c>
+      <c r="H163" s="14" t="s">
+        <v>831</v>
+      </c>
+      <c r="J163" s="14"/>
+      <c r="K163" s="14" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:11">
+      <c r="A164" s="19">
+        <v>64.1</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="C164" s="14" t="s">
+        <v>833</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="E164" s="11"/>
+      <c r="F164" s="12"/>
+      <c r="G164" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="H164" s="18" t="s">
+        <v>836</v>
+      </c>
+      <c r="I164" s="14"/>
+      <c r="J164" s="14"/>
+      <c r="K164" s="14" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="1:11">
+      <c r="A165" s="19">
+        <v>67</v>
+      </c>
+      <c r="B165" s="17">
+        <v>67</v>
+      </c>
+      <c r="C165" s="14" t="s">
+        <v>838</v>
+      </c>
+      <c r="D165" s="11" t="s">
+        <v>839</v>
+      </c>
+      <c r="E165" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="F165" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="G165" s="21" t="s">
+        <v>842</v>
+      </c>
+      <c r="H165" s="18"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="14" t="s">
+        <v>843</v>
+      </c>
+      <c r="K165" s="14"/>
+    </row>
+    <row r="166" customHeight="1" spans="1:11">
+      <c r="A166" s="19">
+        <v>68</v>
+      </c>
+      <c r="B166" s="17">
+        <v>68</v>
+      </c>
+      <c r="C166" s="14" t="s">
+        <v>844</v>
+      </c>
+      <c r="D166" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="E166" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="F166" s="28" t="s">
+        <v>847</v>
+      </c>
+      <c r="G166" s="21" t="s">
+        <v>848</v>
+      </c>
+      <c r="H166" s="18"/>
+      <c r="I166" s="14"/>
+      <c r="J166" s="14" t="s">
+        <v>849</v>
+      </c>
+      <c r="K166" s="14"/>
+    </row>
+    <row r="167" customHeight="1" spans="1:11">
+      <c r="A167" s="19">
+        <v>66</v>
+      </c>
+      <c r="B167" s="17">
+        <v>66</v>
+      </c>
+      <c r="C167" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="D167" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="E167" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="F167" s="27" t="s">
+        <v>852</v>
+      </c>
+      <c r="G167" s="21" t="s">
+        <v>853</v>
+      </c>
+      <c r="H167" s="18" t="s">
+        <v>854</v>
+      </c>
+      <c r="I167" s="14"/>
+      <c r="J167" s="14"/>
+      <c r="K167" s="14" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="1:11">
+      <c r="A168" s="19"/>
+      <c r="B168" s="17"/>
+      <c r="C168" s="14" t="s">
+        <v>856</v>
+      </c>
+      <c r="D168" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="E168" s="11"/>
+      <c r="F168" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G168" s="19" t="s">
+        <v>859</v>
+      </c>
+      <c r="H168" s="18" t="s">
+        <v>860</v>
+      </c>
+      <c r="I168" s="14"/>
+      <c r="J168" s="14"/>
+      <c r="K168" s="14" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="1:11">
+      <c r="A169" s="19"/>
+      <c r="B169" s="17"/>
+      <c r="C169" s="14" t="s">
+        <v>862</v>
+      </c>
+      <c r="D169" s="11" t="s">
+        <v>863</v>
+      </c>
+      <c r="E169" s="11"/>
+      <c r="F169" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G169" s="21" t="s">
+        <v>864</v>
+      </c>
+      <c r="H169" s="18" t="s">
+        <v>865</v>
+      </c>
+      <c r="I169" s="14"/>
+      <c r="J169" s="14"/>
+      <c r="K169" s="14"/>
+    </row>
+    <row r="170" customHeight="1" spans="1:11">
+      <c r="A170" s="19"/>
+      <c r="B170" s="17"/>
+      <c r="C170" s="14" t="s">
+        <v>866</v>
+      </c>
+      <c r="D170" s="11" t="s">
+        <v>867</v>
+      </c>
+      <c r="E170" s="11"/>
+      <c r="F170" s="27" t="s">
+        <v>858</v>
+      </c>
+      <c r="G170" s="21" t="s">
+        <v>868</v>
+      </c>
+      <c r="H170" s="18" t="s">
+        <v>869</v>
+      </c>
+      <c r="I170" s="14"/>
+      <c r="J170" s="14"/>
+      <c r="K170" s="14" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="1:11">
+      <c r="A171" s="19">
+        <v>69</v>
+      </c>
+      <c r="B171" s="17">
+        <v>69</v>
+      </c>
+      <c r="C171" s="14" t="s">
+        <v>871</v>
+      </c>
+      <c r="D171" s="11" t="s">
+        <v>872</v>
+      </c>
+      <c r="E171" s="11" t="s">
+        <v>873</v>
+      </c>
+      <c r="F171" s="16" t="s">
+        <v>874</v>
+      </c>
+      <c r="G171" s="21" t="s">
+        <v>875</v>
+      </c>
+      <c r="H171" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="14"/>
+      <c r="J171" s="14"/>
+      <c r="K171" s="14"/>
+    </row>
+    <row r="172" customHeight="1" spans="1:11">
+      <c r="A172" s="19">
+        <v>70</v>
+      </c>
+      <c r="B172" s="17">
+        <v>70</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>876</v>
+      </c>
+      <c r="D172" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="E172" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="F172" s="16" t="s">
+        <v>878</v>
+      </c>
+      <c r="G172" s="21" t="s">
+        <v>879</v>
+      </c>
+      <c r="H172" s="18" t="s">
+        <v>880</v>
+      </c>
+      <c r="I172" s="14"/>
+      <c r="J172" s="14"/>
+      <c r="K172" s="14"/>
+    </row>
+    <row r="173" customHeight="1" spans="1:11">
+      <c r="A173" s="19"/>
+      <c r="B173" s="23" t="s">
+        <v>881</v>
+      </c>
+      <c r="C173" s="24" t="s">
+        <v>882</v>
+      </c>
+      <c r="D173" s="15" t="s">
+        <v>883</v>
+      </c>
+      <c r="E173" s="15"/>
+      <c r="F173" s="25"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="15"/>
+      <c r="I173" s="15"/>
+      <c r="J173" s="26"/>
+      <c r="K173" s="15"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K152" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:K152">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K173" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:K173">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="C152" r:id="rId1" display="https://www.boosey.com/downloads/schostakowitsch_werkverzeichnis.pdf" tooltip="https://www.boosey.com/downloads/schostakowitsch_werkverzeichnis.pdf"/>
+    <hyperlink ref="C173" r:id="rId1" display="https://www.boosey.com/downloads/schostakowitsch_werkverzeichnis.pdf" tooltip="https://www.boosey.com/downloads/schostakowitsch_werkverzeichnis.pdf"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:K42 A43:F43 H43:K43 A44:K54 A55:F55 H55:K55 A56:K56 A57:F57 H57:K57 A58:K65 A66:F66 H66:K66 A67:K69 A70:F70 H70:K70 A71:K71 A72:F72 H72:K72 A73:K73 A74:F75 H74:K75 A76:K76 A77:F77 H77:K77 A78:K102 A103:F103 H103:K103 A104:K104 A105:F105 H105:K105 A106:K122 A123:F124 H123:K123 H124:J124 A125:K139 A140:F140 H140:K140 A141:K152" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:K160 A161:B161 D161:G161 I161:K161 A162:J163 A164:K164 A165:I166 K165:K166 A167:K167 A168:J168 A169:E169 I169:K169 A170:B170 E170 I170:J170 I171:K171 A173:C173 E173:K173" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8494,7 +9555,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>764</v>
+        <v>884</v>
       </c>
     </row>
   </sheetData>
